--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2094,26 +2094,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>7</v>
-      </c>
       <c r="D52" t="n">
-        <v>140</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2123,29 +2124,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D53" t="n">
-        <v>140</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2155,29 +2157,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2191,25 +2193,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2223,25 +2225,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2251,29 +2253,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2283,29 +2285,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2319,25 +2321,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2351,25 +2353,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2379,29 +2381,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2411,29 +2413,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D62" t="n">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2447,25 +2449,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D63" t="n">
-        <v>39</v>
+        <v>250</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>BE021</t>
         </is>
       </c>
     </row>
@@ -2478,14 +2480,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
       <c r="D64" t="n">
-        <v>250</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>BE021</t>
@@ -2508,17 +2509,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>250</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>BE021</t>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -2573,14 +2573,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -2605,14 +2605,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>172</v>
+        <v>15</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -2733,29 +2733,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>250</v>
+        <v>533.9</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2765,29 +2765,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>250</v>
+        <v>533.9</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2797,29 +2797,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>15</v>
+        <v>533.9</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2833,25 +2833,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>15</v>
+        <v>533.9</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2864,26 +2864,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>8</v>
-      </c>
       <c r="D76" t="n">
-        <v>60</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>116.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2897,25 +2898,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>60</v>
+        <v>116.4</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2928,26 +2929,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>8</v>
-      </c>
       <c r="D78" t="n">
-        <v>15</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>220.9</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2961,25 +2963,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>15</v>
+        <v>220.9</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -2992,26 +2994,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>8</v>
-      </c>
       <c r="D80" t="n">
-        <v>60</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -3025,25 +3028,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>BE022</t>
         </is>
       </c>
     </row>
@@ -3056,13 +3059,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>12</v>
-      </c>
       <c r="D82" t="n">
-        <v>533.9</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3070,7 +3074,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3085,14 +3089,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>533.9</v>
+        <v>268</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
@@ -3102,7 +3106,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3117,16 +3121,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D84" t="n">
-        <v>533.9</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3153,10 +3158,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>533.9</v>
+        <v>218</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
@@ -3166,7 +3171,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3184,14 +3189,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C86" t="n">
+        <v>6</v>
+      </c>
       <c r="D86" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3199,7 +3203,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3218,10 +3222,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>116.4</v>
+        <v>95</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3249,22 +3253,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
       <c r="D88" t="n">
-        <v>220.9</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3283,20 +3286,20 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>220.9</v>
+        <v>120</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3314,14 +3317,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C90" t="n">
+        <v>7</v>
+      </c>
       <c r="D90" t="n">
-        <v>115</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3329,7 +3331,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3348,10 +3350,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
@@ -3361,7 +3363,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3379,14 +3381,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
       <c r="D92" t="n">
-        <v>268</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3394,7 +3395,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3413,10 +3414,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -3426,7 +3427,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3444,22 +3445,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C94" t="n">
+        <v>7</v>
+      </c>
       <c r="D94" t="n">
-        <v>218</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3478,20 +3478,20 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D95" t="n">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D96" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3577,17 +3577,17 @@
         <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>p18</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>p19</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3609,17 +3609,17 @@
         <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>p18</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>p19</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3637,13 +3637,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>7</v>
-      </c>
       <c r="D100" t="n">
-        <v>120</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3651,7 +3652,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -3670,10 +3671,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -3683,7 +3684,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3701,13 +3702,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>7</v>
-      </c>
       <c r="D102" t="n">
-        <v>29</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3715,7 +3717,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3734,10 +3736,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -3747,7 +3749,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -3765,21 +3767,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>7</v>
-      </c>
       <c r="D104" t="n">
-        <v>120</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -3798,20 +3801,20 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3829,13 +3832,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>7</v>
-      </c>
       <c r="D106" t="n">
-        <v>120</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
+        <v>116.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3843,7 +3847,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3862,10 +3866,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>120</v>
+        <v>116.4</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
@@ -3875,7 +3879,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -3893,13 +3897,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>7</v>
-      </c>
       <c r="D108" t="n">
-        <v>29</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
+        <v>220.9</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3907,7 +3912,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3926,10 +3931,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>29</v>
+        <v>220.9</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
@@ -3939,7 +3944,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -3957,27 +3962,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C110" t="n">
+        <v>9</v>
+      </c>
       <c r="D110" t="n">
-        <v>218</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3991,25 +3995,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>218</v>
+        <v>419</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4027,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>115</v>
+        <v>116.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4032,7 +4036,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4042,7 +4046,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4063,12 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>115</v>
+        <v>116.4</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4074,7 +4078,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4092,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>268</v>
+        <v>220.9</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4097,7 +4101,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4107,7 +4111,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4128,12 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>268</v>
+        <v>220.9</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4139,7 +4143,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4157,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>116.4</v>
+        <v>115</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4172,7 +4176,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4193,12 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>116.4</v>
+        <v>115</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4204,7 +4208,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4222,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>220.9</v>
+        <v>268</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4227,7 +4231,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4237,7 +4241,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4258,12 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>220.9</v>
+        <v>268</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4269,7 +4273,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -4282,13 +4286,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>9</v>
-      </c>
       <c r="D120" t="n">
-        <v>419</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -4296,7 +4301,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>419</v>
+        <v>218</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4346,14 +4351,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C122" t="n">
+        <v>6</v>
+      </c>
       <c r="D122" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -4361,7 +4365,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -4380,10 +4384,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>116.4</v>
+        <v>95</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
@@ -4393,7 +4397,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4412,7 +4416,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>220.9</v>
+        <v>218</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4448,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>220.9</v>
+        <v>218</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
@@ -4607,7 +4611,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>218</v>
+        <v>116.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4643,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>218</v>
+        <v>116.4</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
@@ -4671,13 +4675,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>6</v>
-      </c>
       <c r="D132" t="n">
-        <v>95</v>
-      </c>
-      <c r="E132" t="inlineStr"/>
+        <v>220.9</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -4685,7 +4690,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -4704,10 +4709,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>95</v>
+        <v>220.9</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
@@ -4717,7 +4722,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -4735,22 +4740,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C134" t="n">
+        <v>7</v>
+      </c>
       <c r="D134" t="n">
-        <v>218</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -4769,20 +4773,20 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -4800,14 +4804,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C136" t="n">
+        <v>7</v>
+      </c>
       <c r="D136" t="n">
-        <v>115</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -4815,7 +4818,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -4834,10 +4837,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
@@ -4847,7 +4850,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -4865,14 +4868,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C138" t="n">
+        <v>7</v>
+      </c>
       <c r="D138" t="n">
-        <v>268</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -4880,7 +4882,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -4899,10 +4901,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>268</v>
+        <v>33</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
@@ -4912,7 +4914,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -4930,27 +4932,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C140" t="n">
+        <v>7</v>
+      </c>
       <c r="D140" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>134.4</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4964,25 +4965,25 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>116.4</v>
+        <v>134.4</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4995,27 +4996,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C142" t="n">
+        <v>7</v>
+      </c>
       <c r="D142" t="n">
-        <v>220.9</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5029,25 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D143" t="n">
-        <v>220.9</v>
+        <v>220</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5064,22 +5064,22 @@
         <v>7</v>
       </c>
       <c r="D144" t="n">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5096,22 +5096,22 @@
         <v>7</v>
       </c>
       <c r="D145" t="n">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5128,22 +5128,22 @@
         <v>7</v>
       </c>
       <c r="D146" t="n">
-        <v>120</v>
+        <v>90.5</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5160,22 +5160,22 @@
         <v>7</v>
       </c>
       <c r="D147" t="n">
-        <v>120</v>
+        <v>90.5</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5185,29 +5185,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5217,29 +5217,29 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>7</v>
       </c>
       <c r="D149" t="n">
-        <v>33</v>
+        <v>90.5</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5249,14 +5249,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>7</v>
       </c>
       <c r="D150" t="n">
-        <v>134.4</v>
+        <v>90.5</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
@@ -5281,14 +5281,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>7</v>
       </c>
       <c r="D151" t="n">
-        <v>134.4</v>
+        <v>170</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
@@ -5313,14 +5313,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C152" t="n">
         <v>7</v>
       </c>
       <c r="D152" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
@@ -5345,14 +5345,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5377,14 +5377,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>7</v>
       </c>
       <c r="D154" t="n">
-        <v>268</v>
+        <v>90.5</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5409,14 +5409,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>7</v>
       </c>
       <c r="D155" t="n">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -5441,14 +5441,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>7</v>
       </c>
       <c r="D156" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -5485,12 +5485,12 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5512,17 +5512,17 @@
         <v>7</v>
       </c>
       <c r="D158" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D159" t="n">
         <v>90.5</v>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D160" t="n">
         <v>90.5</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -5608,7 +5608,7 @@
         <v>7</v>
       </c>
       <c r="D161" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -5640,7 +5640,7 @@
         <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D163" t="n">
         <v>90.5</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D164" t="n">
         <v>90.5</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -5732,13 +5732,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C165" t="n">
-        <v>7</v>
-      </c>
       <c r="D165" t="n">
-        <v>60</v>
-      </c>
-      <c r="E165" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5746,7 +5747,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -5765,10 +5766,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
@@ -5778,7 +5779,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -5796,21 +5797,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C167" t="n">
-        <v>7</v>
-      </c>
       <c r="D167" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E167" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -5829,20 +5831,20 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -5860,13 +5862,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>6</v>
-      </c>
       <c r="D169" t="n">
         <v>90.5</v>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5874,7 +5877,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -5893,7 +5896,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
         <v>90.5</v>
@@ -5906,7 +5909,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -5928,22 +5931,22 @@
         <v>7</v>
       </c>
       <c r="D171" t="n">
-        <v>50</v>
+        <v>128.7</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5960,22 +5963,22 @@
         <v>7</v>
       </c>
       <c r="D172" t="n">
-        <v>50</v>
+        <v>128.7</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5989,25 +5992,25 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D173" t="n">
-        <v>90.5</v>
+        <v>257.9</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6021,25 +6024,25 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D174" t="n">
-        <v>90.5</v>
+        <v>257.9</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6052,27 +6055,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C175" t="n">
+        <v>7</v>
+      </c>
       <c r="D175" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6082,30 +6084,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>7</v>
       </c>
       <c r="D176" t="n">
-        <v>170</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6115,30 +6116,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>7</v>
       </c>
       <c r="D177" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>128.7</v>
+        <v>90.5</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D179" t="n">
-        <v>128.7</v>
+        <v>90.5</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6219,7 +6219,7 @@
         <v>7</v>
       </c>
       <c r="D180" t="n">
-        <v>257.9</v>
+        <v>170</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6251,7 +6251,7 @@
         <v>7</v>
       </c>
       <c r="D181" t="n">
-        <v>257.9</v>
+        <v>170</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D182" t="n">
-        <v>268</v>
+        <v>90.5</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D183" t="n">
-        <v>268</v>
+        <v>90.5</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6340,14 +6340,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C184" t="n">
         <v>7</v>
       </c>
       <c r="D184" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -6404,14 +6404,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>7</v>
       </c>
       <c r="D186" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6436,14 +6436,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C187" t="n">
         <v>7</v>
       </c>
       <c r="D187" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -6468,24 +6468,24 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C188" t="n">
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D189" t="n">
         <v>90.5</v>
@@ -6512,12 +6512,12 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -6532,14 +6532,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D190" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -6564,14 +6564,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C191" t="n">
         <v>7</v>
       </c>
       <c r="D191" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6596,11 +6596,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D192" t="n">
         <v>90.5</v>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6628,14 +6628,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D193" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6660,16 +6660,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D194" t="n">
-        <v>60</v>
-      </c>
-      <c r="E194" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6677,7 +6678,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -6692,11 +6693,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
         <v>90.5</v>
@@ -6704,12 +6705,12 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -6724,24 +6725,25 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D196" t="n">
         <v>90.5</v>
       </c>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -6756,14 +6758,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -6773,7 +6775,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -6788,16 +6790,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D198" t="n">
         <v>170</v>
       </c>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6805,7 +6808,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -6820,14 +6823,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
@@ -6837,7 +6840,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -6852,29 +6855,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D200" t="n">
-        <v>90.5</v>
+        <v>150</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6884,30 +6887,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>16</v>
       </c>
       <c r="D201" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6920,27 +6922,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C202" t="n">
+        <v>16</v>
+      </c>
       <c r="D202" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>187.5</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6950,30 +6951,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>16</v>
       </c>
       <c r="D203" t="n">
-        <v>170</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>187.5</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7027,7 +7027,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7054,17 +7054,17 @@
         <v>16</v>
       </c>
       <c r="D206" t="n">
-        <v>187.5</v>
+        <v>157.5</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -7086,17 +7086,17 @@
         <v>16</v>
       </c>
       <c r="D207" t="n">
-        <v>187.5</v>
+        <v>157.5</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -7118,17 +7118,17 @@
         <v>16</v>
       </c>
       <c r="D208" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
           <t>p15</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>p7</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7150,17 +7150,17 @@
         <v>16</v>
       </c>
       <c r="D209" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
           <t>p15</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>p7</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7179,20 +7179,20 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D210" t="n">
-        <v>157.5</v>
+        <v>38</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -7211,20 +7211,20 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D211" t="n">
-        <v>157.5</v>
+        <v>38</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D212" t="n">
-        <v>120</v>
+        <v>343</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D213" t="n">
-        <v>120</v>
+        <v>343</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -7303,14 +7303,14 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D214" t="n">
-        <v>38</v>
+        <v>450</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D215" t="n">
-        <v>38</v>
+        <v>450</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -7371,20 +7371,20 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D216" t="n">
-        <v>343</v>
+        <v>164.5</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -7403,20 +7403,20 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D217" t="n">
-        <v>343</v>
+        <v>164.5</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D218" t="n">
-        <v>450</v>
+        <v>197</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D219" t="n">
-        <v>450</v>
+        <v>197</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -7502,7 +7502,7 @@
         <v>7</v>
       </c>
       <c r="D220" t="n">
-        <v>164.5</v>
+        <v>197</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -7534,7 +7534,7 @@
         <v>7</v>
       </c>
       <c r="D221" t="n">
-        <v>164.5</v>
+        <v>197</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -7566,7 +7566,7 @@
         <v>7</v>
       </c>
       <c r="D222" t="n">
-        <v>197</v>
+        <v>164.5</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -7598,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="D223" t="n">
-        <v>197</v>
+        <v>164.5</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -7612,134 +7612,6 @@
         </is>
       </c>
       <c r="H223" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>223</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
-        <v>7</v>
-      </c>
-      <c r="D224" t="n">
-        <v>197</v>
-      </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>p143</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>224</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
-        <v>7</v>
-      </c>
-      <c r="D225" t="n">
-        <v>197</v>
-      </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>p143</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>225</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C226" t="n">
-        <v>7</v>
-      </c>
-      <c r="D226" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>226</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C227" t="n">
-        <v>7</v>
-      </c>
-      <c r="D227" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
         <is>
           <t>CO009</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
         <v>250</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
         <v>250</v>
@@ -2484,7 +2484,7 @@
         <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -2516,7 +2516,7 @@
         <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -2580,7 +2580,7 @@
         <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -2612,7 +2612,7 @@
         <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
@@ -2644,7 +2644,7 @@
         <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -2676,7 +2676,7 @@
         <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -2708,7 +2708,7 @@
         <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>231.4</v>
+        <v>438.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>231.4</v>
+        <v>438.9</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>438.9</v>
+        <v>268</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>438.9</v>
+        <v>268</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>268</v>
+        <v>231.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="D81" t="n">
-        <v>268</v>
+        <v>231.4</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>231.4</v>
+        <v>268</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>231.4</v>
+        <v>268</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>268</v>
+        <v>231.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>7</v>
       </c>
       <c r="D101" t="n">
-        <v>268</v>
+        <v>231.4</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>7</v>
       </c>
       <c r="D117" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
@@ -4409,29 +4409,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D124" t="n">
-        <v>134.4</v>
+        <v>210</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4445,25 +4445,25 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>134.4</v>
+        <v>210</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4517,12 +4517,12 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4544,17 +4544,17 @@
         <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>268</v>
+        <v>134.4</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -4576,17 +4576,17 @@
         <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>268</v>
+        <v>134.4</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4608,17 +4608,17 @@
         <v>7</v>
       </c>
       <c r="D130" t="n">
-        <v>90.5</v>
+        <v>268</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -4640,17 +4640,17 @@
         <v>7</v>
       </c>
       <c r="D131" t="n">
-        <v>90.5</v>
+        <v>268</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -4665,24 +4665,24 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>7</v>
       </c>
       <c r="D132" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
+          <t>p101</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
           <t>p124</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>p47</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -4709,12 +4709,12 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -4736,7 +4736,7 @@
         <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>90.5</v>
+        <v>172</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -4768,7 +4768,7 @@
         <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
@@ -4800,7 +4800,7 @@
         <v>7</v>
       </c>
       <c r="D136" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
@@ -4832,7 +4832,7 @@
         <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -4864,7 +4864,7 @@
         <v>7</v>
       </c>
       <c r="D138" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -4896,7 +4896,7 @@
         <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
@@ -4928,7 +4928,7 @@
         <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -4960,12 +4960,12 @@
         <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -4992,12 +4992,12 @@
         <v>7</v>
       </c>
       <c r="D142" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D143" t="n">
         <v>90.5</v>
@@ -5029,12 +5029,12 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D144" t="n">
         <v>90.5</v>
@@ -5061,12 +5061,12 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D145" t="n">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D146" t="n">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D147" t="n">
-        <v>90.5</v>
+        <v>50</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>90.5</v>
+        <v>50</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5212,14 +5212,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C149" t="n">
+        <v>9</v>
+      </c>
       <c r="D149" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5227,7 +5226,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -5242,17 +5241,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5260,7 +5258,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5275,16 +5273,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D151" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E151" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5307,16 +5306,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D152" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E152" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5339,17 +5339,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>9</v>
       </c>
       <c r="D153" t="n">
-        <v>170</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5372,17 +5371,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>170</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5405,16 +5403,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D155" t="n">
-        <v>170</v>
-      </c>
-      <c r="E155" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5437,16 +5436,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D156" t="n">
-        <v>170</v>
-      </c>
-      <c r="E156" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5469,17 +5469,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>7</v>
       </c>
       <c r="D157" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5502,17 +5501,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>7</v>
       </c>
       <c r="D158" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5535,16 +5533,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D159" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E159" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5567,16 +5566,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D160" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E160" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5599,29 +5599,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D161" t="n">
-        <v>313</v>
+        <v>116</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5635,25 +5635,25 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D162" t="n">
-        <v>313</v>
+        <v>116</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
         <v>7</v>
       </c>
       <c r="D163" t="n">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
@@ -5702,7 +5702,7 @@
         <v>7</v>
       </c>
       <c r="D164" t="n">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
@@ -5734,7 +5734,7 @@
         <v>7</v>
       </c>
       <c r="D165" t="n">
-        <v>318</v>
+        <v>95.5</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
@@ -5766,7 +5766,7 @@
         <v>7</v>
       </c>
       <c r="D166" t="n">
-        <v>318</v>
+        <v>95.5</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D172" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D173" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -6022,7 +6022,7 @@
         <v>7</v>
       </c>
       <c r="D174" t="n">
-        <v>110</v>
+        <v>90.5</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
@@ -6054,7 +6054,7 @@
         <v>7</v>
       </c>
       <c r="D175" t="n">
-        <v>110</v>
+        <v>90.5</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
@@ -6150,7 +6150,7 @@
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>110</v>
+        <v>90.5</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
@@ -6182,7 +6182,7 @@
         <v>7</v>
       </c>
       <c r="D179" t="n">
-        <v>110</v>
+        <v>90.5</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
@@ -6214,7 +6214,7 @@
         <v>7</v>
       </c>
       <c r="D180" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -6246,7 +6246,7 @@
         <v>7</v>
       </c>
       <c r="D181" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D182" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D183" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D186" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D187" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D190" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -6567,10 +6567,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D191" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D194" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D195" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
@@ -6801,12 +6801,12 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -6833,12 +6833,12 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -6860,17 +6860,17 @@
         <v>16</v>
       </c>
       <c r="D200" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -6892,17 +6892,17 @@
         <v>16</v>
       </c>
       <c r="D201" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -6924,7 +6924,7 @@
         <v>16</v>
       </c>
       <c r="D202" t="n">
-        <v>300</v>
+        <v>157.5</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
@@ -6956,7 +6956,7 @@
         <v>16</v>
       </c>
       <c r="D203" t="n">
-        <v>300</v>
+        <v>157.5</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
@@ -6988,7 +6988,7 @@
         <v>16</v>
       </c>
       <c r="D204" t="n">
-        <v>157.5</v>
+        <v>120</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -7020,7 +7020,7 @@
         <v>16</v>
       </c>
       <c r="D205" t="n">
-        <v>157.5</v>
+        <v>120</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -7369,25 +7369,25 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D216" t="n">
-        <v>197</v>
+        <v>133.3</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7397,29 +7397,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>197</v>
+        <v>133.3</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7433,25 +7433,25 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>164.5</v>
+        <v>133.3</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7465,25 +7465,2826 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D219" t="n">
-        <v>164.5</v>
+        <v>133.3</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>9</v>
+      </c>
+      <c r="D220" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>9</v>
+      </c>
+      <c r="D221" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>10</v>
+      </c>
+      <c r="D222" t="n">
+        <v>208</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>7</v>
+      </c>
+      <c r="D223" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>7</v>
+      </c>
+      <c r="D224" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>7</v>
+      </c>
+      <c r="D225" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>7</v>
+      </c>
+      <c r="D226" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>7</v>
+      </c>
+      <c r="D227" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>7</v>
+      </c>
+      <c r="D228" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>12</v>
+      </c>
+      <c r="D229" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>12</v>
+      </c>
+      <c r="D230" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>12</v>
+      </c>
+      <c r="D231" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>12</v>
+      </c>
+      <c r="D232" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>12</v>
+      </c>
+      <c r="D233" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>12</v>
+      </c>
+      <c r="D234" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>12</v>
+      </c>
+      <c r="D235" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>12</v>
+      </c>
+      <c r="D236" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>12</v>
+      </c>
+      <c r="D237" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>12</v>
+      </c>
+      <c r="D238" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>12</v>
+      </c>
+      <c r="D239" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>12</v>
+      </c>
+      <c r="D240" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>12</v>
+      </c>
+      <c r="D241" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>12</v>
+      </c>
+      <c r="D242" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>12</v>
+      </c>
+      <c r="D243" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>12</v>
+      </c>
+      <c r="D244" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>12</v>
+      </c>
+      <c r="D245" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>12</v>
+      </c>
+      <c r="D246" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>8</v>
+      </c>
+      <c r="D250" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>8</v>
+      </c>
+      <c r="D251" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>8</v>
+      </c>
+      <c r="D252" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>12</v>
+      </c>
+      <c r="D253" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>12</v>
+      </c>
+      <c r="D254" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>12</v>
+      </c>
+      <c r="D255" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>12</v>
+      </c>
+      <c r="D256" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>12</v>
+      </c>
+      <c r="D257" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>12</v>
+      </c>
+      <c r="D258" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>7</v>
+      </c>
+      <c r="D263" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>7</v>
+      </c>
+      <c r="D264" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>7</v>
+      </c>
+      <c r="D265" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>7</v>
+      </c>
+      <c r="D266" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>12</v>
+      </c>
+      <c r="D267" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>12</v>
+      </c>
+      <c r="D268" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>12</v>
+      </c>
+      <c r="D269" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>12</v>
+      </c>
+      <c r="D270" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>12</v>
+      </c>
+      <c r="D271" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>12</v>
+      </c>
+      <c r="D272" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>12</v>
+      </c>
+      <c r="D273" t="n">
+        <v>60</v>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>12</v>
+      </c>
+      <c r="D274" t="n">
+        <v>60</v>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>8</v>
+      </c>
+      <c r="D276" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>9</v>
+      </c>
+      <c r="D277" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>9</v>
+      </c>
+      <c r="D278" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>9</v>
+      </c>
+      <c r="D279" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>9</v>
+      </c>
+      <c r="D280" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>9</v>
+      </c>
+      <c r="D281" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>9</v>
+      </c>
+      <c r="D282" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>9</v>
+      </c>
+      <c r="D283" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>9</v>
+      </c>
+      <c r="D284" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>9</v>
+      </c>
+      <c r="D285" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>9</v>
+      </c>
+      <c r="D286" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>9</v>
+      </c>
+      <c r="D287" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>9</v>
+      </c>
+      <c r="D288" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>7</v>
+      </c>
+      <c r="D291" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>7</v>
+      </c>
+      <c r="D292" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>7</v>
+      </c>
+      <c r="D295" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>7</v>
+      </c>
+      <c r="D296" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>7</v>
+      </c>
+      <c r="D299" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>7</v>
+      </c>
+      <c r="D300" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>200</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>200</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>200</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>8</v>
+      </c>
+      <c r="D304" t="n">
+        <v>200</v>
+      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>8</v>
+      </c>
+      <c r="D305" t="n">
+        <v>200</v>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>8</v>
+      </c>
+      <c r="D306" t="n">
+        <v>200</v>
+      </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>CO010</t>
         </is>
       </c>
     </row>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7244,7 +7244,7 @@
         <v>7</v>
       </c>
       <c r="D212" t="n">
-        <v>164.5</v>
+        <v>190</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -7276,7 +7276,7 @@
         <v>7</v>
       </c>
       <c r="D213" t="n">
-        <v>164.5</v>
+        <v>190</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
@@ -7308,7 +7308,7 @@
         <v>7</v>
       </c>
       <c r="D214" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
@@ -7340,7 +7340,7 @@
         <v>7</v>
       </c>
       <c r="D215" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
@@ -7369,25 +7369,25 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D216" t="n">
-        <v>133.3</v>
+        <v>190</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7397,29 +7397,29 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D217" t="n">
-        <v>133.3</v>
+        <v>190</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
         <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>133.3</v>
+        <v>216</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C219" t="n">
         <v>9</v>
       </c>
       <c r="D219" t="n">
-        <v>133.3</v>
+        <v>216</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C220" t="n">
         <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>133.3</v>
+        <v>216</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -7532,7 +7532,7 @@
         <v>9</v>
       </c>
       <c r="D221" t="n">
-        <v>133.3</v>
+        <v>216</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D222" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D223" t="n">
-        <v>206.7</v>
+        <v>216</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D224" t="n">
-        <v>206.7</v>
+        <v>208</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -7660,7 +7660,7 @@
         <v>7</v>
       </c>
       <c r="D225" t="n">
-        <v>173.3</v>
+        <v>207</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
@@ -7692,7 +7692,7 @@
         <v>7</v>
       </c>
       <c r="D226" t="n">
-        <v>173.3</v>
+        <v>207</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
@@ -7724,7 +7724,7 @@
         <v>7</v>
       </c>
       <c r="D227" t="n">
-        <v>92.7</v>
+        <v>109</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -7756,7 +7756,7 @@
         <v>7</v>
       </c>
       <c r="D228" t="n">
-        <v>92.7</v>
+        <v>109</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D229" t="n">
-        <v>78.59999999999999</v>
+        <v>109</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D230" t="n">
-        <v>78.59999999999999</v>
+        <v>109</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -7852,7 +7852,7 @@
         <v>12</v>
       </c>
       <c r="D231" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -7884,7 +7884,7 @@
         <v>12</v>
       </c>
       <c r="D232" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
@@ -7916,7 +7916,7 @@
         <v>12</v>
       </c>
       <c r="D233" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -7948,7 +7948,7 @@
         <v>12</v>
       </c>
       <c r="D234" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -7980,7 +7980,7 @@
         <v>12</v>
       </c>
       <c r="D235" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -8012,7 +8012,7 @@
         <v>12</v>
       </c>
       <c r="D236" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -8044,7 +8044,7 @@
         <v>12</v>
       </c>
       <c r="D237" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
@@ -8076,7 +8076,7 @@
         <v>12</v>
       </c>
       <c r="D238" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -8108,7 +8108,7 @@
         <v>12</v>
       </c>
       <c r="D239" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -8140,7 +8140,7 @@
         <v>12</v>
       </c>
       <c r="D240" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -8172,7 +8172,7 @@
         <v>12</v>
       </c>
       <c r="D241" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -8204,7 +8204,7 @@
         <v>12</v>
       </c>
       <c r="D242" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -8236,7 +8236,7 @@
         <v>12</v>
       </c>
       <c r="D243" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8268,7 +8268,7 @@
         <v>12</v>
       </c>
       <c r="D244" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8300,7 +8300,7 @@
         <v>12</v>
       </c>
       <c r="D245" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -8332,7 +8332,7 @@
         <v>12</v>
       </c>
       <c r="D246" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -8360,14 +8360,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C247" t="n">
+        <v>12</v>
+      </c>
       <c r="D247" t="n">
         <v>92.7</v>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8390,17 +8389,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>12</v>
       </c>
       <c r="D248" t="n">
         <v>92.7</v>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8427,7 +8425,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>92.7</v>
+        <v>90</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8456,16 +8454,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D250" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E250" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8488,16 +8487,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D251" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E251" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8527,7 +8527,7 @@
         <v>8</v>
       </c>
       <c r="D252" t="n">
-        <v>92.7</v>
+        <v>90</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -8552,14 +8552,14 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D253" t="n">
-        <v>58.7</v>
+        <v>90</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8584,14 +8584,14 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D254" t="n">
-        <v>58.7</v>
+        <v>90</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -8744,17 +8744,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>12</v>
       </c>
       <c r="D259" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8762,7 +8761,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8777,17 +8776,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>12</v>
       </c>
       <c r="D260" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8795,7 +8793,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -8876,16 +8874,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D263" t="n">
         <v>92.7</v>
       </c>
-      <c r="E263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F263" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8908,16 +8907,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D264" t="n">
         <v>92.7</v>
       </c>
-      <c r="E264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8940,16 +8940,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D265" t="n">
         <v>92.7</v>
       </c>
-      <c r="E265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9004,14 +9005,14 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D267" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9021,7 +9022,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9036,14 +9037,14 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D268" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
@@ -9053,7 +9054,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9068,14 +9069,14 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D269" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -9085,7 +9086,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9104,10 +9105,10 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D270" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
@@ -9117,7 +9118,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9132,7 +9133,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -9164,7 +9165,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -9203,7 +9204,7 @@
         <v>12</v>
       </c>
       <c r="D273" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9213,7 +9214,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9235,7 +9236,7 @@
         <v>12</v>
       </c>
       <c r="D274" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9245,7 +9246,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9260,17 +9261,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>12</v>
       </c>
       <c r="D275" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D276" t="n">
-        <v>233.3</v>
+        <v>58.7</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D277" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9361,10 +9361,10 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D278" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9392,13 +9392,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C279" t="n">
-        <v>9</v>
-      </c>
       <c r="D279" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E279" t="inlineStr"/>
+        <v>233.3</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9406,7 +9407,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9425,10 +9426,10 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D280" t="n">
-        <v>92.7</v>
+        <v>233.3</v>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
@@ -9438,7 +9439,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9712,14 +9713,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C289" t="n">
+        <v>9</v>
+      </c>
       <c r="D289" t="n">
         <v>73.3</v>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -9742,17 +9742,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>9</v>
       </c>
       <c r="D290" t="n">
         <v>73.3</v>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9760,7 +9759,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -9775,14 +9774,14 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D291" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -9792,7 +9791,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -9811,10 +9810,10 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D292" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -9824,7 +9823,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -9843,7 +9842,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9876,7 +9875,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9905,16 +9904,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D295" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E295" t="inlineStr"/>
+        <v>73.3</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9944,7 +9944,7 @@
         <v>7</v>
       </c>
       <c r="D296" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
@@ -9969,17 +9969,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>7</v>
       </c>
       <c r="D297" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>73.3</v>
+      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10002,17 +10001,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>7</v>
       </c>
       <c r="D298" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>73.3</v>
+      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10035,16 +10033,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D299" t="n">
         <v>92.7</v>
       </c>
-      <c r="E299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10067,16 +10066,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D300" t="n">
         <v>92.7</v>
       </c>
-      <c r="E300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>200</v>
+        <v>92.7</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -10132,17 +10132,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>7</v>
       </c>
       <c r="D302" t="n">
-        <v>200</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10150,7 +10149,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -10165,17 +10164,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>7</v>
       </c>
       <c r="D303" t="n">
-        <v>200</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10183,7 +10181,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -10202,10 +10200,10 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D304" t="n">
-        <v>200</v>
+        <v>92.7</v>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
@@ -10215,7 +10213,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -10230,16 +10228,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D305" t="n">
-        <v>200</v>
-      </c>
-      <c r="E305" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10247,7 +10246,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -10262,27 +10261,352 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>7</v>
+      </c>
+      <c r="D308" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>7</v>
+      </c>
+      <c r="D309" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>7</v>
+      </c>
+      <c r="D310" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>200</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>200</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>200</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
         <v>8</v>
       </c>
-      <c r="D306" t="n">
+      <c r="D314" t="n">
         <v>200</v>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
         <is>
           <t>p197</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>8</v>
+      </c>
+      <c r="D315" t="n">
+        <v>200</v>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>8</v>
+      </c>
+      <c r="D316" t="n">
+        <v>200</v>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
         <is>
           <t>CO010</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>438.9</v>
+        <v>140</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>438.9</v>
+        <v>140</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>231.4</v>
+        <v>140</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="D81" t="n">
-        <v>231.4</v>
+        <v>140</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>438.9</v>
+        <v>140</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>438.9</v>
+        <v>140</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>231.4</v>
+        <v>140</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>7</v>
       </c>
       <c r="D101" t="n">
-        <v>231.4</v>
+        <v>140</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -4224,7 +4224,7 @@
         <v>7</v>
       </c>
       <c r="D118" t="n">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
@@ -4256,7 +4256,7 @@
         <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
@@ -4288,17 +4288,17 @@
         <v>7</v>
       </c>
       <c r="D120" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4320,17 +4320,17 @@
         <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4352,17 +4352,17 @@
         <v>7</v>
       </c>
       <c r="D122" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -4384,17 +4384,17 @@
         <v>7</v>
       </c>
       <c r="D123" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4485,12 +4485,12 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
+          <t>CO007</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
           <t>p101</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>p124</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4517,12 +4517,12 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
+          <t>CO007</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
           <t>p101</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>p124</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4544,7 +4544,7 @@
         <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>134.4</v>
+        <v>268</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
@@ -4576,7 +4576,7 @@
         <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>134.4</v>
+        <v>268</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
@@ -4608,7 +4608,7 @@
         <v>7</v>
       </c>
       <c r="D130" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -4640,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="D131" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5727,14 +5727,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>7</v>
       </c>
       <c r="D165" t="n">
-        <v>95.5</v>
+        <v>172</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -5759,14 +5759,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>7</v>
       </c>
       <c r="D166" t="n">
-        <v>95.5</v>
+        <v>90.5</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -5798,7 +5798,7 @@
         <v>7</v>
       </c>
       <c r="D167" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -5830,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
@@ -5862,7 +5862,7 @@
         <v>7</v>
       </c>
       <c r="D169" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D170" t="n">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D171" t="n">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D172" t="n">
-        <v>116</v>
+        <v>90.5</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D173" t="n">
-        <v>116</v>
+        <v>90.5</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6022,7 +6022,7 @@
         <v>7</v>
       </c>
       <c r="D174" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
@@ -6054,7 +6054,7 @@
         <v>7</v>
       </c>
       <c r="D175" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
@@ -6086,12 +6086,12 @@
         <v>7</v>
       </c>
       <c r="D176" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6118,12 +6118,12 @@
         <v>7</v>
       </c>
       <c r="D177" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6150,17 +6150,17 @@
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -6182,17 +6182,17 @@
         <v>7</v>
       </c>
       <c r="D179" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D181" t="n">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
@@ -6274,13 +6274,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C182" t="n">
-        <v>9</v>
-      </c>
       <c r="D182" t="n">
         <v>116</v>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6288,7 +6289,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6303,16 +6304,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D183" t="n">
         <v>116</v>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6320,7 +6322,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6335,17 +6337,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>9</v>
       </c>
       <c r="D184" t="n">
         <v>116</v>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6368,17 +6369,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>9</v>
       </c>
       <c r="D185" t="n">
         <v>116</v>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6401,16 +6401,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D186" t="n">
         <v>116</v>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6433,16 +6434,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D187" t="n">
         <v>116</v>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6465,17 +6467,16 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>9</v>
       </c>
       <c r="D188" t="n">
         <v>116</v>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6498,17 +6499,16 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>9</v>
       </c>
       <c r="D189" t="n">
         <v>116</v>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6531,16 +6531,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D190" t="n">
-        <v>116</v>
-      </c>
-      <c r="E190" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6563,16 +6564,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D191" t="n">
-        <v>116</v>
-      </c>
-      <c r="E191" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6595,17 +6597,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>7</v>
       </c>
       <c r="D192" t="n">
         <v>220</v>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6628,17 +6629,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>7</v>
       </c>
       <c r="D193" t="n">
         <v>220</v>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6661,29 +6661,29 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D194" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6697,25 +6697,25 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D195" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6732,17 +6732,17 @@
         <v>16</v>
       </c>
       <c r="D196" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -6764,17 +6764,17 @@
         <v>16</v>
       </c>
       <c r="D197" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -6796,7 +6796,7 @@
         <v>16</v>
       </c>
       <c r="D198" t="n">
-        <v>187.5</v>
+        <v>150</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -6828,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="D199" t="n">
-        <v>187.5</v>
+        <v>150</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -6860,7 +6860,7 @@
         <v>16</v>
       </c>
       <c r="D200" t="n">
-        <v>150</v>
+        <v>157.5</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -6892,7 +6892,7 @@
         <v>16</v>
       </c>
       <c r="D201" t="n">
-        <v>150</v>
+        <v>157.5</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -6924,7 +6924,7 @@
         <v>16</v>
       </c>
       <c r="D202" t="n">
-        <v>157.5</v>
+        <v>120</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -6956,7 +6956,7 @@
         <v>16</v>
       </c>
       <c r="D203" t="n">
-        <v>157.5</v>
+        <v>120</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -6985,20 +6985,20 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D204" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -7017,20 +7017,20 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D205" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D206" t="n">
-        <v>70</v>
+        <v>604</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D207" t="n">
-        <v>70</v>
+        <v>604</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D208" t="n">
-        <v>604</v>
+        <v>450</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D209" t="n">
-        <v>604</v>
+        <v>450</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7173,24 +7173,24 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D210" t="n">
-        <v>450</v>
+        <v>164.5</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -7209,20 +7209,20 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D211" t="n">
-        <v>450</v>
+        <v>164.5</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -7244,7 +7244,7 @@
         <v>7</v>
       </c>
       <c r="D212" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -7276,7 +7276,7 @@
         <v>7</v>
       </c>
       <c r="D213" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
@@ -7305,25 +7305,25 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D214" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7333,29 +7333,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D215" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7369,25 +7369,25 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D216" t="n">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7401,25 +7401,25 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO010</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D220" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D221" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D222" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D223" t="n">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D224" t="n">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -7660,7 +7660,7 @@
         <v>7</v>
       </c>
       <c r="D225" t="n">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
@@ -7692,7 +7692,7 @@
         <v>7</v>
       </c>
       <c r="D226" t="n">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D227" t="n">
-        <v>109</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D228" t="n">
-        <v>109</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D229" t="n">
-        <v>109</v>
+        <v>73.3</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D230" t="n">
-        <v>109</v>
+        <v>73.3</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -7852,7 +7852,7 @@
         <v>12</v>
       </c>
       <c r="D231" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -7884,7 +7884,7 @@
         <v>12</v>
       </c>
       <c r="D232" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -7916,7 +7916,7 @@
         <v>12</v>
       </c>
       <c r="D233" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
@@ -7948,7 +7948,7 @@
         <v>12</v>
       </c>
       <c r="D234" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
@@ -7980,7 +7980,7 @@
         <v>12</v>
       </c>
       <c r="D235" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -8012,7 +8012,7 @@
         <v>12</v>
       </c>
       <c r="D236" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -8044,7 +8044,7 @@
         <v>12</v>
       </c>
       <c r="D237" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -8076,7 +8076,7 @@
         <v>12</v>
       </c>
       <c r="D238" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -8108,7 +8108,7 @@
         <v>12</v>
       </c>
       <c r="D239" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -8140,7 +8140,7 @@
         <v>12</v>
       </c>
       <c r="D240" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8172,7 +8172,7 @@
         <v>12</v>
       </c>
       <c r="D241" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -8204,7 +8204,7 @@
         <v>12</v>
       </c>
       <c r="D242" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -8236,7 +8236,7 @@
         <v>12</v>
       </c>
       <c r="D243" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -8268,7 +8268,7 @@
         <v>12</v>
       </c>
       <c r="D244" t="n">
-        <v>78.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -8296,13 +8296,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C245" t="n">
-        <v>12</v>
-      </c>
       <c r="D245" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E245" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8310,7 +8311,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -8325,16 +8326,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D246" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E246" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F246" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8342,7 +8344,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -8360,13 +8362,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C247" t="n">
-        <v>12</v>
-      </c>
       <c r="D247" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E247" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F247" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8393,10 +8396,10 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D248" t="n">
-        <v>92.7</v>
+        <v>90</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8421,17 +8424,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>8</v>
       </c>
       <c r="D249" t="n">
         <v>90</v>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8454,17 +8456,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>8</v>
       </c>
       <c r="D250" t="n">
         <v>90</v>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8490,14 +8491,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C251" t="n">
+        <v>12</v>
+      </c>
       <c r="D251" t="n">
-        <v>90</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8520,14 +8520,14 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D252" t="n">
-        <v>90</v>
+        <v>58.7</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -8552,14 +8552,14 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D253" t="n">
-        <v>90</v>
+        <v>58.7</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8588,10 +8588,10 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D254" t="n">
-        <v>90</v>
+        <v>58.7</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -8683,13 +8683,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C257" t="n">
-        <v>12</v>
-      </c>
       <c r="D257" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="E257" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F257" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8697,7 +8698,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -8712,16 +8713,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D258" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="E258" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8729,7 +8731,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -8744,16 +8746,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D259" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="E259" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F259" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8761,7 +8764,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8776,16 +8779,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C260" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D260" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="E260" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F260" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8793,7 +8797,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -8841,17 +8845,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>7</v>
       </c>
       <c r="D262" t="n">
         <v>92.7</v>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8874,17 +8877,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>7</v>
       </c>
       <c r="D263" t="n">
         <v>92.7</v>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8907,17 +8909,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>7</v>
       </c>
       <c r="D264" t="n">
         <v>92.7</v>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8940,17 +8941,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>7</v>
       </c>
       <c r="D265" t="n">
         <v>92.7</v>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9005,14 +9005,14 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D267" t="n">
-        <v>92.7</v>
+        <v>58.7</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9037,14 +9037,14 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D268" t="n">
-        <v>92.7</v>
+        <v>58.7</v>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D269" t="n">
-        <v>92.7</v>
+        <v>58.7</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D270" t="n">
-        <v>92.7</v>
+        <v>58.7</v>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -9204,7 +9204,7 @@
         <v>12</v>
       </c>
       <c r="D273" t="n">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9236,7 +9236,7 @@
         <v>12</v>
       </c>
       <c r="D274" t="n">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9261,16 +9261,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D275" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="E275" t="inlineStr"/>
+        <v>233.3</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9278,7 +9279,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9297,10 +9298,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D276" t="n">
-        <v>58.7</v>
+        <v>233.3</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9310,7 +9311,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9329,10 +9330,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D277" t="n">
-        <v>60</v>
+        <v>106.7</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9342,7 +9343,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9361,10 +9362,10 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D278" t="n">
-        <v>60</v>
+        <v>106.7</v>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
@@ -9374,7 +9375,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9392,14 +9393,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C279" t="n">
+        <v>9</v>
+      </c>
       <c r="D279" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D280" t="n">
-        <v>233.3</v>
+        <v>92.7</v>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9525,7 +9525,7 @@
         <v>9</v>
       </c>
       <c r="D283" t="n">
-        <v>92.7</v>
+        <v>106.7</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -9557,7 +9557,7 @@
         <v>9</v>
       </c>
       <c r="D284" t="n">
-        <v>92.7</v>
+        <v>106.7</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -9589,7 +9589,7 @@
         <v>9</v>
       </c>
       <c r="D285" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -9621,7 +9621,7 @@
         <v>9</v>
       </c>
       <c r="D286" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -9653,7 +9653,7 @@
         <v>9</v>
       </c>
       <c r="D287" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -9685,7 +9685,7 @@
         <v>9</v>
       </c>
       <c r="D288" t="n">
-        <v>92.7</v>
+        <v>73.3</v>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -9717,7 +9717,7 @@
         <v>9</v>
       </c>
       <c r="D289" t="n">
-        <v>73.3</v>
+        <v>106.7</v>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
@@ -9749,7 +9749,7 @@
         <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>73.3</v>
+        <v>106.7</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -9841,14 +9841,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C293" t="n">
+        <v>9</v>
+      </c>
       <c r="D293" t="n">
         <v>73.3</v>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9856,7 +9855,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -9871,17 +9870,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>9</v>
       </c>
       <c r="D294" t="n">
         <v>73.3</v>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9889,7 +9887,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -9937,16 +9935,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D296" t="n">
         <v>73.3</v>
       </c>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9969,16 +9968,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D297" t="n">
         <v>73.3</v>
       </c>
-      <c r="E297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F297" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10033,17 +10033,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>7</v>
       </c>
       <c r="D299" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>73.3</v>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10066,17 +10065,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>7</v>
       </c>
       <c r="D300" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>73.3</v>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10132,16 +10130,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D302" t="n">
         <v>92.7</v>
       </c>
-      <c r="E302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10164,16 +10163,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D303" t="n">
         <v>92.7</v>
       </c>
-      <c r="E303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10228,17 +10228,16 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>7</v>
       </c>
       <c r="D305" t="n">
         <v>92.7</v>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10261,17 +10260,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>7</v>
       </c>
       <c r="D306" t="n">
         <v>92.7</v>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10327,16 +10325,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D308" t="n">
         <v>92.7</v>
       </c>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10359,16 +10358,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D309" t="n">
         <v>92.7</v>
       </c>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10423,17 +10423,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>7</v>
       </c>
       <c r="D311" t="n">
-        <v>200</v>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10441,7 +10440,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -10456,17 +10455,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>7</v>
       </c>
       <c r="D312" t="n">
-        <v>200</v>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10474,7 +10472,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -10522,16 +10520,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D314" t="n">
         <v>200</v>
       </c>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10554,16 +10553,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D315" t="n">
         <v>200</v>
       </c>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10607,6 +10607,70 @@
         </is>
       </c>
       <c r="H316" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>8</v>
+      </c>
+      <c r="D317" t="n">
+        <v>200</v>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>8</v>
+      </c>
+      <c r="D318" t="n">
+        <v>200</v>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
         <is>
           <t>CO010</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H367"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6150,22 +6150,22 @@
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6175,29 +6175,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>7</v>
       </c>
       <c r="D179" t="n">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
         <v>7</v>
       </c>
       <c r="D180" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6246,7 +6246,7 @@
         <v>7</v>
       </c>
       <c r="D181" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6278,7 +6278,7 @@
         <v>7</v>
       </c>
       <c r="D182" t="n">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
@@ -6310,7 +6310,7 @@
         <v>7</v>
       </c>
       <c r="D183" t="n">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -6342,7 +6342,7 @@
         <v>7</v>
       </c>
       <c r="D184" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="D185" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
@@ -6406,7 +6406,7 @@
         <v>7</v>
       </c>
       <c r="D186" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6438,7 +6438,7 @@
         <v>7</v>
       </c>
       <c r="D187" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -6470,7 +6470,7 @@
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
@@ -6502,7 +6502,7 @@
         <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D190" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D191" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D192" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D193" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6662,7 +6662,7 @@
         <v>7</v>
       </c>
       <c r="D194" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
@@ -6694,7 +6694,7 @@
         <v>7</v>
       </c>
       <c r="D195" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
@@ -6726,12 +6726,12 @@
         <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -6758,12 +6758,12 @@
         <v>7</v>
       </c>
       <c r="D197" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -6790,17 +6790,17 @@
         <v>7</v>
       </c>
       <c r="D198" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -6822,17 +6822,17 @@
         <v>7</v>
       </c>
       <c r="D199" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D200" t="n">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -6883,10 +6883,10 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D201" t="n">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -6914,14 +6914,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C202" t="n">
+        <v>9</v>
+      </c>
       <c r="D202" t="n">
         <v>116</v>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6929,7 +6928,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -6944,17 +6943,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>9</v>
       </c>
       <c r="D203" t="n">
         <v>116</v>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6962,7 +6960,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -6977,16 +6975,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D204" t="n">
         <v>116</v>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7009,16 +7008,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D205" t="n">
         <v>116</v>
       </c>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7041,17 +7041,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>9</v>
       </c>
       <c r="D206" t="n">
         <v>116</v>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7074,17 +7073,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>9</v>
       </c>
       <c r="D207" t="n">
         <v>116</v>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7107,16 +7105,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D208" t="n">
         <v>116</v>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7139,16 +7138,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D209" t="n">
         <v>116</v>
       </c>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7171,17 +7171,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>220</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7204,17 +7203,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>9</v>
       </c>
       <c r="D211" t="n">
-        <v>220</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7237,16 +7235,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D212" t="n">
         <v>220</v>
       </c>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7269,16 +7268,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D213" t="n">
         <v>220</v>
       </c>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7301,29 +7301,29 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D214" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7337,25 +7337,25 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D215" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7372,17 +7372,17 @@
         <v>16</v>
       </c>
       <c r="D216" t="n">
-        <v>187.5</v>
+        <v>150</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -7404,17 +7404,17 @@
         <v>16</v>
       </c>
       <c r="D217" t="n">
-        <v>187.5</v>
+        <v>150</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -7436,7 +7436,7 @@
         <v>16</v>
       </c>
       <c r="D218" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -7468,7 +7468,7 @@
         <v>16</v>
       </c>
       <c r="D219" t="n">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -7500,7 +7500,7 @@
         <v>16</v>
       </c>
       <c r="D220" t="n">
-        <v>157.5</v>
+        <v>150</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
@@ -7532,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="D221" t="n">
-        <v>157.5</v>
+        <v>150</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
@@ -7564,7 +7564,7 @@
         <v>16</v>
       </c>
       <c r="D222" t="n">
-        <v>120</v>
+        <v>157.5</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -7596,7 +7596,7 @@
         <v>16</v>
       </c>
       <c r="D223" t="n">
-        <v>120</v>
+        <v>157.5</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -7625,20 +7625,20 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D224" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -7657,20 +7657,20 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D225" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -7689,10 +7689,10 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D226" t="n">
-        <v>604</v>
+        <v>38</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D227" t="n">
-        <v>604</v>
+        <v>38</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D228" t="n">
-        <v>450</v>
+        <v>343</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D229" t="n">
-        <v>450</v>
+        <v>343</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -7877,24 +7877,24 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D232" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -7913,20 +7913,20 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D233" t="n">
-        <v>190</v>
+        <v>450</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -7948,7 +7948,7 @@
         <v>7</v>
       </c>
       <c r="D234" t="n">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
@@ -7980,7 +7980,7 @@
         <v>7</v>
       </c>
       <c r="D235" t="n">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
@@ -8012,12 +8012,12 @@
         <v>7</v>
       </c>
       <c r="D236" t="n">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -8044,12 +8044,12 @@
         <v>7</v>
       </c>
       <c r="D237" t="n">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -8073,25 +8073,25 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D238" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8101,29 +8101,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D239" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
         <v>9</v>
       </c>
       <c r="D240" t="n">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8165,14 +8165,14 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C241" t="n">
         <v>9</v>
       </c>
       <c r="D241" t="n">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8197,14 +8197,14 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C242" t="n">
         <v>9</v>
       </c>
       <c r="D242" t="n">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8236,7 +8236,7 @@
         <v>9</v>
       </c>
       <c r="D243" t="n">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D244" t="n">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D245" t="n">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -8520,13 +8520,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C252" t="n">
-        <v>12</v>
-      </c>
       <c r="D252" t="n">
-        <v>120.5</v>
-      </c>
-      <c r="E252" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8534,7 +8535,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -8549,16 +8550,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D253" t="n">
-        <v>120.5</v>
-      </c>
-      <c r="E253" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8566,7 +8568,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -8584,13 +8586,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C254" t="n">
-        <v>12</v>
-      </c>
       <c r="D254" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="E254" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8598,7 +8601,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -8617,10 +8620,10 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D255" t="n">
-        <v>15.3</v>
+        <v>90</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -8630,7 +8633,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -8645,14 +8648,14 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D256" t="n">
-        <v>92.7</v>
+        <v>90</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -8662,7 +8665,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -8681,10 +8684,10 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D257" t="n">
-        <v>92.7</v>
+        <v>90</v>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
@@ -8694,7 +8697,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -8716,7 +8719,7 @@
         <v>12</v>
       </c>
       <c r="D258" t="n">
-        <v>199.3</v>
+        <v>58.7</v>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
@@ -8726,7 +8729,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -8741,14 +8744,14 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C259" t="n">
         <v>12</v>
       </c>
       <c r="D259" t="n">
-        <v>199.3</v>
+        <v>58.7</v>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
@@ -8758,7 +8761,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8790,7 +8793,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -8822,7 +8825,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -8837,14 +8840,14 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C262" t="n">
         <v>12</v>
       </c>
       <c r="D262" t="n">
-        <v>26.2</v>
+        <v>58.7</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -8854,7 +8857,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -8876,7 +8879,7 @@
         <v>12</v>
       </c>
       <c r="D263" t="n">
-        <v>26.2</v>
+        <v>58.7</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
@@ -8886,7 +8889,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -8905,7 +8908,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8919,7 +8922,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -8938,7 +8941,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8952,7 +8955,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -8971,7 +8974,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8985,7 +8988,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -9000,16 +9003,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D267" t="n">
-        <v>90</v>
-      </c>
-      <c r="E267" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9017,7 +9021,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9032,16 +9036,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D268" t="n">
-        <v>90</v>
-      </c>
-      <c r="E268" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F268" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9049,7 +9054,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9068,10 +9073,10 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D269" t="n">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -9081,7 +9086,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9096,14 +9101,14 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D270" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
@@ -9113,7 +9118,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9128,14 +9133,14 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D271" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9145,7 +9150,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -9160,14 +9165,14 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D272" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9177,7 +9182,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -9196,10 +9201,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D273" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9209,7 +9214,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9224,7 +9229,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -9241,7 +9246,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9256,7 +9261,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -9273,7 +9278,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9291,14 +9296,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C276" t="n">
+        <v>12</v>
+      </c>
       <c r="D276" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9306,7 +9310,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9321,17 +9325,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>12</v>
       </c>
       <c r="D277" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9339,7 +9342,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9354,17 +9357,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>12</v>
       </c>
       <c r="D278" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9372,7 +9374,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9387,17 +9389,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>12</v>
       </c>
       <c r="D279" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9405,7 +9406,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9423,14 +9424,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C280" t="n">
+        <v>12</v>
+      </c>
       <c r="D280" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D281" t="n">
-        <v>92.7</v>
+        <v>60</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -9485,16 +9485,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D282" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E282" t="inlineStr"/>
+        <v>233.3</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9502,7 +9503,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -9521,10 +9522,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D283" t="n">
-        <v>92.7</v>
+        <v>233.3</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9534,7 +9535,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -9549,14 +9550,14 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D284" t="n">
-        <v>92.7</v>
+        <v>112.7</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9566,7 +9567,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -9585,10 +9586,10 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D285" t="n">
-        <v>92.7</v>
+        <v>112.7</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -9598,7 +9599,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -9617,10 +9618,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D286" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -9630,7 +9631,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -9645,14 +9646,14 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D287" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
@@ -9662,7 +9663,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -9681,10 +9682,10 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D288" t="n">
-        <v>58.7</v>
+        <v>206.7</v>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
@@ -9694,7 +9695,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -9713,10 +9714,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D289" t="n">
-        <v>58.7</v>
+        <v>206.7</v>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
@@ -9726,7 +9727,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -9741,14 +9742,14 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>58.7</v>
+        <v>173.3</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -9758,7 +9759,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -9777,10 +9778,10 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D291" t="n">
-        <v>58.7</v>
+        <v>173.3</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -9790,7 +9791,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -9809,10 +9810,10 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D292" t="n">
-        <v>60</v>
+        <v>112.7</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -9822,7 +9823,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -9841,10 +9842,10 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D293" t="n">
-        <v>60</v>
+        <v>112.7</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -9854,7 +9855,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -9872,14 +9873,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C294" t="n">
+        <v>9</v>
+      </c>
       <c r="D294" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -9906,10 +9906,10 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D295" t="n">
-        <v>233.3</v>
+        <v>92.7</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -9941,7 +9941,7 @@
         <v>9</v>
       </c>
       <c r="D296" t="n">
-        <v>233.3</v>
+        <v>206.7</v>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -9973,7 +9973,7 @@
         <v>9</v>
       </c>
       <c r="D297" t="n">
-        <v>233.3</v>
+        <v>206.7</v>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -10005,7 +10005,7 @@
         <v>9</v>
       </c>
       <c r="D298" t="n">
-        <v>112.7</v>
+        <v>173.3</v>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -10037,7 +10037,7 @@
         <v>9</v>
       </c>
       <c r="D299" t="n">
-        <v>112.7</v>
+        <v>173.3</v>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -10069,7 +10069,7 @@
         <v>9</v>
       </c>
       <c r="D300" t="n">
-        <v>233.3</v>
+        <v>112.7</v>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -10101,7 +10101,7 @@
         <v>9</v>
       </c>
       <c r="D301" t="n">
-        <v>233.3</v>
+        <v>112.7</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -10133,7 +10133,7 @@
         <v>9</v>
       </c>
       <c r="D302" t="n">
-        <v>112.7</v>
+        <v>92.7</v>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -10165,7 +10165,7 @@
         <v>9</v>
       </c>
       <c r="D303" t="n">
-        <v>112.7</v>
+        <v>92.7</v>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -10197,7 +10197,7 @@
         <v>9</v>
       </c>
       <c r="D304" t="n">
-        <v>208</v>
+        <v>206.7</v>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -10229,7 +10229,7 @@
         <v>9</v>
       </c>
       <c r="D305" t="n">
-        <v>208</v>
+        <v>206.7</v>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -10261,7 +10261,7 @@
         <v>9</v>
       </c>
       <c r="D306" t="n">
-        <v>92.7</v>
+        <v>173.3</v>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
@@ -10293,7 +10293,7 @@
         <v>9</v>
       </c>
       <c r="D307" t="n">
-        <v>92.7</v>
+        <v>173.3</v>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
@@ -10321,13 +10321,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C308" t="n">
-        <v>9</v>
-      </c>
       <c r="D308" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E308" t="inlineStr"/>
+        <v>73.3</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F308" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10335,7 +10336,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -10350,16 +10351,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D309" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E309" t="inlineStr"/>
+        <v>73.3</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F309" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10367,7 +10369,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -10385,13 +10387,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C310" t="n">
-        <v>9</v>
-      </c>
       <c r="D310" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="E310" t="inlineStr"/>
+        <v>73.3</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10399,7 +10402,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -10418,10 +10421,10 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D311" t="n">
-        <v>173.3</v>
+        <v>73.3</v>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
@@ -10431,7 +10434,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -10446,14 +10449,14 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D312" t="n">
-        <v>233.3</v>
+        <v>73.3</v>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
@@ -10463,7 +10466,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -10482,10 +10485,10 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D313" t="n">
-        <v>233.3</v>
+        <v>73.3</v>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
@@ -10495,7 +10498,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -10513,13 +10516,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C314" t="n">
-        <v>9</v>
-      </c>
       <c r="D314" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E314" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10527,7 +10531,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -10542,16 +10546,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D315" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E315" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10559,7 +10564,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -10577,13 +10582,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C316" t="n">
-        <v>9</v>
-      </c>
       <c r="D316" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E316" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10591,7 +10597,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -10610,10 +10616,10 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D317" t="n">
-        <v>233.3</v>
+        <v>92.7</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10623,7 +10629,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -10638,14 +10644,14 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D318" t="n">
-        <v>112.7</v>
+        <v>92.7</v>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
@@ -10655,7 +10661,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -10674,10 +10680,10 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D319" t="n">
-        <v>112.7</v>
+        <v>92.7</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -10687,7 +10693,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -10705,13 +10711,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C320" t="n">
-        <v>9</v>
-      </c>
       <c r="D320" t="n">
-        <v>208</v>
-      </c>
-      <c r="E320" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F320" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10719,7 +10726,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -10734,16 +10741,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D321" t="n">
-        <v>208</v>
-      </c>
-      <c r="E321" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F321" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10751,7 +10759,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -10769,13 +10777,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C322" t="n">
-        <v>9</v>
-      </c>
       <c r="D322" t="n">
         <v>92.7</v>
       </c>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F322" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10783,7 +10792,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -10802,7 +10811,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D323" t="n">
         <v>92.7</v>
@@ -10815,7 +10824,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -10830,14 +10839,14 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D324" t="n">
-        <v>206.7</v>
+        <v>92.7</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -10847,7 +10856,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -10866,10 +10875,10 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D325" t="n">
-        <v>206.7</v>
+        <v>92.7</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -10879,7 +10888,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -10897,13 +10906,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C326" t="n">
-        <v>9</v>
-      </c>
       <c r="D326" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="E326" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F326" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10926,16 +10936,17 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D327" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="E327" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F327" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10961,13 +10972,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C328" t="n">
-        <v>9</v>
-      </c>
       <c r="D328" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E328" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F328" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10975,7 +10987,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -10994,10 +11006,10 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D329" t="n">
-        <v>233.3</v>
+        <v>200</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11007,7 +11019,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -11022,14 +11034,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D330" t="n">
-        <v>112.7</v>
+        <v>200</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11039,7 +11051,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -11058,10 +11070,10 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D331" t="n">
-        <v>112.7</v>
+        <v>200</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -11071,1174 +11083,10 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>331</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>9</v>
-      </c>
-      <c r="D332" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>332</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C333" t="n">
-        <v>9</v>
-      </c>
-      <c r="D333" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>333</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C334" t="n">
-        <v>9</v>
-      </c>
-      <c r="D334" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>334</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>9</v>
-      </c>
-      <c r="D335" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>335</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C336" t="n">
-        <v>9</v>
-      </c>
-      <c r="D336" t="n">
-        <v>208</v>
-      </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>336</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C337" t="n">
-        <v>9</v>
-      </c>
-      <c r="D337" t="n">
-        <v>208</v>
-      </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>337</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C338" t="n">
-        <v>9</v>
-      </c>
-      <c r="D338" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>338</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>9</v>
-      </c>
-      <c r="D339" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>339</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>9</v>
-      </c>
-      <c r="D340" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>340</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>9</v>
-      </c>
-      <c r="D341" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>341</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>9</v>
-      </c>
-      <c r="D342" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>342</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>9</v>
-      </c>
-      <c r="D343" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>343</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D344" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>344</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D345" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>345</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D346" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>346</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>7</v>
-      </c>
-      <c r="D347" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>347</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>7</v>
-      </c>
-      <c r="D348" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>348</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>7</v>
-      </c>
-      <c r="D349" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>349</v>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D350" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>350</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D351" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>351</v>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D352" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>352</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>7</v>
-      </c>
-      <c r="D353" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>353</v>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>7</v>
-      </c>
-      <c r="D354" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>354</v>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>7</v>
-      </c>
-      <c r="D355" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>355</v>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D356" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>356</v>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D357" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>357</v>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D358" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>358</v>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>7</v>
-      </c>
-      <c r="D359" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>359</v>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>7</v>
-      </c>
-      <c r="D360" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>360</v>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>7</v>
-      </c>
-      <c r="D361" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>361</v>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D362" t="n">
-        <v>200</v>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>362</v>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D363" t="n">
-        <v>200</v>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>363</v>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D364" t="n">
-        <v>200</v>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>364</v>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>8</v>
-      </c>
-      <c r="D365" t="n">
-        <v>200</v>
-      </c>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>365</v>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>8</v>
-      </c>
-      <c r="D366" t="n">
-        <v>200</v>
-      </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>366</v>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>8</v>
-      </c>
-      <c r="D367" t="n">
-        <v>200</v>
-      </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
         <is>
           <t>CO010</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11087,6 +11087,390 @@
         </is>
       </c>
       <c r="H331" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>12</v>
+      </c>
+      <c r="D332" t="n">
+        <v>120</v>
+      </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>12</v>
+      </c>
+      <c r="D333" t="n">
+        <v>120</v>
+      </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>7</v>
+      </c>
+      <c r="D334" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>p196</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>7</v>
+      </c>
+      <c r="D335" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>p196</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>8</v>
+      </c>
+      <c r="D336" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>8</v>
+      </c>
+      <c r="D337" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>8</v>
+      </c>
+      <c r="D338" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>8</v>
+      </c>
+      <c r="D339" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>8</v>
+      </c>
+      <c r="D340" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>8</v>
+      </c>
+      <c r="D341" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>8</v>
+      </c>
+      <c r="D342" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>p169</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>8</v>
+      </c>
+      <c r="D343" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>p169</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
         <is>
           <t>CO010</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H343"/>
+  <dimension ref="A1:H453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3706,7 +3706,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
@@ -3738,7 +3738,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
@@ -4224,7 +4224,7 @@
         <v>7</v>
       </c>
       <c r="D118" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
@@ -4256,7 +4256,7 @@
         <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
@@ -4288,7 +4288,7 @@
         <v>7</v>
       </c>
       <c r="D120" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
@@ -4320,7 +4320,7 @@
         <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -4800,17 +4800,17 @@
         <v>7</v>
       </c>
       <c r="D136" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -4832,17 +4832,17 @@
         <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -4928,7 +4928,7 @@
         <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -4960,7 +4960,7 @@
         <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
@@ -4992,17 +4992,17 @@
         <v>7</v>
       </c>
       <c r="D142" t="n">
-        <v>90.5</v>
+        <v>268</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
+          <t>CO007</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
           <t>p101</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>p124</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5024,17 +5024,17 @@
         <v>7</v>
       </c>
       <c r="D143" t="n">
-        <v>90.5</v>
+        <v>268</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
+          <t>CO007</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
           <t>p101</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>p124</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6211,25 +6211,25 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D180" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6239,29 +6239,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D181" t="n">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6275,25 +6275,25 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D182" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6307,25 +6307,25 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D183" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6339,25 +6339,25 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D184" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6371,25 +6371,25 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D185" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
         <v>7</v>
       </c>
       <c r="D186" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6438,7 +6438,7 @@
         <v>7</v>
       </c>
       <c r="D187" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -6470,7 +6470,7 @@
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -6502,7 +6502,7 @@
         <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -6534,7 +6534,7 @@
         <v>7</v>
       </c>
       <c r="D190" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -6566,7 +6566,7 @@
         <v>7</v>
       </c>
       <c r="D191" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D192" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D193" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -6726,7 +6726,7 @@
         <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -6758,7 +6758,7 @@
         <v>7</v>
       </c>
       <c r="D197" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -6787,20 +6787,20 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D198" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -6819,20 +6819,20 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D199" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -6854,7 +6854,7 @@
         <v>7</v>
       </c>
       <c r="D200" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>7</v>
       </c>
       <c r="D201" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D202" t="n">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D203" t="n">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -6978,22 +6978,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C204" t="n">
+        <v>7</v>
+      </c>
       <c r="D204" t="n">
-        <v>116</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -7008,25 +7007,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>7</v>
       </c>
       <c r="D205" t="n">
-        <v>116</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -7041,14 +7039,14 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D206" t="n">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -7058,7 +7056,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -7077,10 +7075,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D207" t="n">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
@@ -7090,7 +7088,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -7108,14 +7106,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C208" t="n">
+        <v>9</v>
+      </c>
       <c r="D208" t="n">
         <v>116</v>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7123,7 +7120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7138,17 +7135,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>9</v>
       </c>
       <c r="D209" t="n">
         <v>116</v>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7156,7 +7152,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7171,16 +7167,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D210" t="n">
         <v>116</v>
       </c>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7203,16 +7200,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D211" t="n">
         <v>116</v>
       </c>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7235,17 +7233,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>9</v>
       </c>
       <c r="D212" t="n">
-        <v>220</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7268,17 +7265,16 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>9</v>
       </c>
       <c r="D213" t="n">
-        <v>220</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7301,16 +7297,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D214" t="n">
-        <v>220</v>
-      </c>
-      <c r="E214" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7333,16 +7330,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D215" t="n">
-        <v>220</v>
-      </c>
-      <c r="E215" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -7365,29 +7363,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D216" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7401,25 +7399,25 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7432,26 +7430,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C218" t="n">
-        <v>16</v>
-      </c>
       <c r="D218" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="E218" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7461,29 +7460,30 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
-        <v>16</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D219" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="E219" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7493,29 +7493,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D220" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7529,25 +7529,25 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D221" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7561,25 +7561,25 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D222" t="n">
-        <v>157.5</v>
+        <v>115.5</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7593,25 +7593,25 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D223" t="n">
-        <v>157.5</v>
+        <v>115.5</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7625,25 +7625,25 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D224" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7657,25 +7657,25 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D225" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7689,25 +7689,25 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D226" t="n">
-        <v>38</v>
+        <v>90.5</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7721,25 +7721,25 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D227" t="n">
-        <v>38</v>
+        <v>90.5</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7753,25 +7753,25 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D228" t="n">
-        <v>343</v>
+        <v>50</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7785,25 +7785,25 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>343</v>
+        <v>50</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
         <v>16</v>
       </c>
       <c r="D230" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>16</v>
       </c>
       <c r="D231" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -7877,24 +7877,24 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C232" t="n">
         <v>16</v>
       </c>
       <c r="D232" t="n">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -7916,17 +7916,17 @@
         <v>16</v>
       </c>
       <c r="D233" t="n">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -7945,20 +7945,20 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D234" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -7977,20 +7977,20 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D235" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -8009,20 +8009,20 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D236" t="n">
-        <v>222</v>
+        <v>157.5</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -8041,20 +8041,20 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D237" t="n">
-        <v>222</v>
+        <v>157.5</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -8073,20 +8073,20 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D238" t="n">
-        <v>190</v>
+        <v>187.5</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -8105,20 +8105,20 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D239" t="n">
-        <v>190</v>
+        <v>187.5</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -8137,25 +8137,25 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D240" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8165,29 +8165,29 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D241" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8201,25 +8201,25 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D242" t="n">
-        <v>133</v>
+        <v>343</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8233,25 +8233,25 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D243" t="n">
-        <v>133</v>
+        <v>343</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8261,29 +8261,29 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D244" t="n">
-        <v>133</v>
+        <v>405</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8293,29 +8293,29 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D245" t="n">
-        <v>133</v>
+        <v>405</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8325,29 +8325,29 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D246" t="n">
-        <v>207</v>
+        <v>405</v>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8361,25 +8361,25 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D247" t="n">
-        <v>207</v>
+        <v>405</v>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8396,22 +8396,22 @@
         <v>7</v>
       </c>
       <c r="D248" t="n">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8428,22 +8428,22 @@
         <v>7</v>
       </c>
       <c r="D249" t="n">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8460,22 +8460,22 @@
         <v>7</v>
       </c>
       <c r="D250" t="n">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8492,22 +8492,22 @@
         <v>7</v>
       </c>
       <c r="D251" t="n">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8520,27 +8520,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C252" t="n">
+        <v>7</v>
+      </c>
       <c r="D252" t="n">
-        <v>90</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8550,30 +8549,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>7</v>
       </c>
       <c r="D253" t="n">
-        <v>90</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8586,27 +8584,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C254" t="n">
+        <v>16</v>
+      </c>
       <c r="D254" t="n">
-        <v>90</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8620,25 +8617,25 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D255" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8648,29 +8645,29 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D256" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8684,25 +8681,25 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D257" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8716,25 +8713,25 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D258" t="n">
-        <v>58.7</v>
+        <v>164.5</v>
       </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8744,29 +8741,29 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D259" t="n">
-        <v>58.7</v>
+        <v>164.5</v>
       </c>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8780,25 +8777,25 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D260" t="n">
-        <v>58.7</v>
+        <v>157.5</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8812,25 +8809,25 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D261" t="n">
-        <v>58.7</v>
+        <v>157.5</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8840,14 +8837,14 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>58.7</v>
+        <v>133.3</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -8857,7 +8854,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -8872,14 +8869,14 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D263" t="n">
-        <v>58.7</v>
+        <v>133.3</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
@@ -8889,7 +8886,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -8907,14 +8904,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C264" t="n">
+        <v>9</v>
+      </c>
       <c r="D264" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>133.3</v>
+      </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8922,7 +8918,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -8937,17 +8933,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>9</v>
       </c>
       <c r="D265" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>133.3</v>
+      </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8955,7 +8950,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -8970,17 +8965,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>9</v>
       </c>
       <c r="D266" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>133.3</v>
+      </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8988,7 +8982,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -9003,17 +8997,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>9</v>
       </c>
       <c r="D267" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>133.3</v>
+      </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9021,7 +9014,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9039,14 +9032,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C268" t="n">
+        <v>10</v>
+      </c>
       <c r="D268" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9054,7 +9046,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9069,14 +9061,14 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D269" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -9086,7 +9078,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9101,14 +9093,14 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D270" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
@@ -9118,7 +9110,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9137,10 +9129,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D271" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9150,7 +9142,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -9169,10 +9161,10 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D272" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9182,7 +9174,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -9201,10 +9193,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D273" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9214,7 +9206,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9233,10 +9225,10 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D274" t="n">
-        <v>58.7</v>
+        <v>164</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9246,7 +9238,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9261,14 +9253,14 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D275" t="n">
-        <v>58.7</v>
+        <v>164</v>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
@@ -9278,7 +9270,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9297,10 +9289,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D276" t="n">
-        <v>58.7</v>
+        <v>164</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9310,7 +9302,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9329,10 +9321,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D277" t="n">
-        <v>58.7</v>
+        <v>164</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9342,7 +9334,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9357,14 +9349,14 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D278" t="n">
-        <v>58.7</v>
+        <v>164</v>
       </c>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
@@ -9374,7 +9366,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9393,10 +9385,10 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D279" t="n">
-        <v>58.7</v>
+        <v>164</v>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
@@ -9406,7 +9398,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9424,13 +9416,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C280" t="n">
-        <v>12</v>
-      </c>
       <c r="D280" t="n">
-        <v>60</v>
-      </c>
-      <c r="E280" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9438,7 +9431,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9453,16 +9446,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D281" t="n">
-        <v>60</v>
-      </c>
-      <c r="E281" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9470,7 +9464,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -9489,7 +9483,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>233.3</v>
+        <v>121</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -9503,7 +9497,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -9522,10 +9516,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D283" t="n">
-        <v>233.3</v>
+        <v>121</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9535,7 +9529,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -9550,14 +9544,14 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D284" t="n">
-        <v>112.7</v>
+        <v>121</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9567,7 +9561,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -9586,10 +9580,10 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D285" t="n">
-        <v>112.7</v>
+        <v>121</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -9599,7 +9593,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -9618,10 +9612,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D286" t="n">
-        <v>92.7</v>
+        <v>121</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -9646,14 +9640,14 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D287" t="n">
-        <v>92.7</v>
+        <v>121</v>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
@@ -9682,10 +9676,10 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D288" t="n">
-        <v>206.7</v>
+        <v>121</v>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
@@ -9714,10 +9708,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D289" t="n">
-        <v>206.7</v>
+        <v>121</v>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
@@ -9742,14 +9736,14 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D290" t="n">
-        <v>173.3</v>
+        <v>121</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -9778,10 +9772,10 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D291" t="n">
-        <v>173.3</v>
+        <v>121</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -9809,13 +9803,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C292" t="n">
-        <v>9</v>
-      </c>
       <c r="D292" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E292" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9823,7 +9818,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -9838,16 +9833,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D293" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="E293" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9855,7 +9851,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -9870,14 +9866,14 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D294" t="n">
-        <v>92.7</v>
+        <v>143</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -9887,7 +9883,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -9906,10 +9902,10 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D295" t="n">
-        <v>92.7</v>
+        <v>143</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -9919,7 +9915,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -9938,10 +9934,10 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D296" t="n">
-        <v>206.7</v>
+        <v>138</v>
       </c>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
@@ -9951,7 +9947,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -9966,14 +9962,14 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D297" t="n">
-        <v>206.7</v>
+        <v>138</v>
       </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
@@ -9983,7 +9979,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -10002,10 +9998,10 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D298" t="n">
-        <v>173.3</v>
+        <v>138</v>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
@@ -10015,7 +10011,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -10034,10 +10030,10 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D299" t="n">
-        <v>173.3</v>
+        <v>138</v>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
@@ -10047,7 +10043,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -10062,14 +10058,14 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D300" t="n">
-        <v>112.7</v>
+        <v>138</v>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
@@ -10079,7 +10075,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -10098,10 +10094,10 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D301" t="n">
-        <v>112.7</v>
+        <v>138</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -10111,7 +10107,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -10133,7 +10129,7 @@
         <v>9</v>
       </c>
       <c r="D302" t="n">
-        <v>92.7</v>
+        <v>233.3</v>
       </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
@@ -10143,7 +10139,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -10165,7 +10161,7 @@
         <v>9</v>
       </c>
       <c r="D303" t="n">
-        <v>92.7</v>
+        <v>233.3</v>
       </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
@@ -10175,7 +10171,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -10197,7 +10193,7 @@
         <v>9</v>
       </c>
       <c r="D304" t="n">
-        <v>206.7</v>
+        <v>112.7</v>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
@@ -10207,7 +10203,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -10229,7 +10225,7 @@
         <v>9</v>
       </c>
       <c r="D305" t="n">
-        <v>206.7</v>
+        <v>112.7</v>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
@@ -10239,7 +10235,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -10261,7 +10257,7 @@
         <v>9</v>
       </c>
       <c r="D306" t="n">
-        <v>173.3</v>
+        <v>92.7</v>
       </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
@@ -10293,7 +10289,7 @@
         <v>9</v>
       </c>
       <c r="D307" t="n">
-        <v>173.3</v>
+        <v>92.7</v>
       </c>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
@@ -10321,14 +10317,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C308" t="n">
+        <v>9</v>
+      </c>
       <c r="D308" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>206.7</v>
+      </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10336,7 +10331,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -10351,17 +10346,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>9</v>
       </c>
       <c r="D309" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>206.7</v>
+      </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10369,7 +10363,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -10387,14 +10381,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C310" t="n">
+        <v>9</v>
+      </c>
       <c r="D310" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>173.3</v>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10402,7 +10395,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -10421,10 +10414,10 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D311" t="n">
-        <v>73.3</v>
+        <v>173.3</v>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
@@ -10434,7 +10427,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -10449,14 +10442,14 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D312" t="n">
-        <v>73.3</v>
+        <v>233.3</v>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
@@ -10466,7 +10459,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -10485,10 +10478,10 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D313" t="n">
-        <v>73.3</v>
+        <v>233.3</v>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
@@ -10498,7 +10491,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -10516,14 +10509,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C314" t="n">
+        <v>9</v>
+      </c>
       <c r="D314" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>112.7</v>
+      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10531,7 +10523,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -10546,17 +10538,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>9</v>
       </c>
       <c r="D315" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>112.7</v>
+      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10564,7 +10555,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -10582,14 +10573,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C316" t="n">
+        <v>9</v>
+      </c>
       <c r="D316" t="n">
         <v>92.7</v>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10597,7 +10587,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -10616,7 +10606,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D317" t="n">
         <v>92.7</v>
@@ -10629,7 +10619,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -10644,14 +10634,14 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D318" t="n">
-        <v>92.7</v>
+        <v>206.7</v>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
@@ -10661,7 +10651,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -10680,10 +10670,10 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D319" t="n">
-        <v>92.7</v>
+        <v>206.7</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -10693,7 +10683,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -10711,14 +10701,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C320" t="n">
+        <v>9</v>
+      </c>
       <c r="D320" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>173.3</v>
+      </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10726,7 +10715,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -10741,17 +10730,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>9</v>
       </c>
       <c r="D321" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>173.3</v>
+      </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10759,7 +10747,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -10777,14 +10765,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C322" t="n">
+        <v>9</v>
+      </c>
       <c r="D322" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>233.3</v>
+      </c>
+      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10792,7 +10779,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -10811,10 +10798,10 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D323" t="n">
-        <v>92.7</v>
+        <v>233.3</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -10824,7 +10811,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -10839,14 +10826,14 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D324" t="n">
-        <v>92.7</v>
+        <v>112.7</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -10856,7 +10843,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -10875,10 +10862,10 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D325" t="n">
-        <v>92.7</v>
+        <v>112.7</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -10888,7 +10875,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -10906,14 +10893,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C326" t="n">
+        <v>9</v>
+      </c>
       <c r="D326" t="n">
-        <v>200</v>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10936,17 +10922,16 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>9</v>
       </c>
       <c r="D327" t="n">
-        <v>200</v>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>92.7</v>
+      </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10972,14 +10957,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C328" t="n">
+        <v>9</v>
+      </c>
       <c r="D328" t="n">
-        <v>200</v>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>206.7</v>
+      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11006,10 +10990,10 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D329" t="n">
-        <v>200</v>
+        <v>206.7</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11034,14 +11018,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D330" t="n">
-        <v>200</v>
+        <v>173.3</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11070,10 +11054,10 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D331" t="n">
-        <v>200</v>
+        <v>173.3</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -11101,13 +11085,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C332" t="n">
-        <v>12</v>
-      </c>
       <c r="D332" t="n">
-        <v>120</v>
-      </c>
-      <c r="E332" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11115,7 +11100,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -11130,14 +11115,14 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D333" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -11147,7 +11132,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -11165,13 +11150,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C334" t="n">
-        <v>7</v>
-      </c>
       <c r="D334" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E334" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F334" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11179,7 +11165,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>p196</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -11194,14 +11180,14 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C335" t="n">
         <v>7</v>
       </c>
       <c r="D335" t="n">
-        <v>206.7</v>
+        <v>147</v>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
@@ -11211,7 +11197,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>p196</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -11229,13 +11215,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C336" t="n">
-        <v>8</v>
-      </c>
       <c r="D336" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="E336" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F336" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11243,7 +11230,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -11258,14 +11245,14 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D337" t="n">
-        <v>109.3</v>
+        <v>147</v>
       </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
@@ -11275,7 +11262,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -11293,13 +11280,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C338" t="n">
-        <v>8</v>
-      </c>
       <c r="D338" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E338" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F338" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11307,7 +11295,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -11325,13 +11313,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C339" t="n">
-        <v>8</v>
-      </c>
       <c r="D339" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="E339" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F339" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11339,7 +11328,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -11357,13 +11346,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C340" t="n">
-        <v>8</v>
-      </c>
       <c r="D340" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E340" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F340" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -11371,7 +11361,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -11386,14 +11376,14 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D341" t="n">
-        <v>233.3</v>
+        <v>121</v>
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
@@ -11403,7 +11393,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -11418,14 +11408,14 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D342" t="n">
-        <v>266.7</v>
+        <v>121</v>
       </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
@@ -11435,7 +11425,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>p169</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -11450,14 +11440,14 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D343" t="n">
-        <v>266.7</v>
+        <v>121</v>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
@@ -11467,10 +11457,3530 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>p169</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>7</v>
+      </c>
+      <c r="D344" t="n">
+        <v>139</v>
+      </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>7</v>
+      </c>
+      <c r="D345" t="n">
+        <v>139</v>
+      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>7</v>
+      </c>
+      <c r="D346" t="n">
+        <v>139</v>
+      </c>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>7</v>
+      </c>
+      <c r="D347" t="n">
+        <v>139</v>
+      </c>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>8</v>
+      </c>
+      <c r="D348" t="n">
+        <v>147</v>
+      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>8</v>
+      </c>
+      <c r="D349" t="n">
+        <v>147</v>
+      </c>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>8</v>
+      </c>
+      <c r="D350" t="n">
+        <v>147</v>
+      </c>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>8</v>
+      </c>
+      <c r="D351" t="n">
+        <v>147</v>
+      </c>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>8</v>
+      </c>
+      <c r="D352" t="n">
+        <v>260</v>
+      </c>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>8</v>
+      </c>
+      <c r="D353" t="n">
+        <v>260</v>
+      </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>8</v>
+      </c>
+      <c r="D354" t="n">
+        <v>175</v>
+      </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>8</v>
+      </c>
+      <c r="D355" t="n">
+        <v>175</v>
+      </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>8</v>
+      </c>
+      <c r="D356" t="n">
+        <v>175</v>
+      </c>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>8</v>
+      </c>
+      <c r="D357" t="n">
+        <v>175</v>
+      </c>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>7</v>
+      </c>
+      <c r="D358" t="n">
+        <v>139</v>
+      </c>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>p196</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>7</v>
+      </c>
+      <c r="D359" t="n">
+        <v>139</v>
+      </c>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>p196</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>7</v>
+      </c>
+      <c r="D360" t="n">
+        <v>139</v>
+      </c>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>p196</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>7</v>
+      </c>
+      <c r="D361" t="n">
+        <v>139</v>
+      </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>p196</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>7</v>
+      </c>
+      <c r="D362" t="n">
+        <v>260</v>
+      </c>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>7</v>
+      </c>
+      <c r="D363" t="n">
+        <v>260</v>
+      </c>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>7</v>
+      </c>
+      <c r="D364" t="n">
+        <v>147</v>
+      </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>7</v>
+      </c>
+      <c r="D365" t="n">
+        <v>147</v>
+      </c>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>7</v>
+      </c>
+      <c r="D366" t="n">
+        <v>147</v>
+      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>7</v>
+      </c>
+      <c r="D367" t="n">
+        <v>147</v>
+      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>7</v>
+      </c>
+      <c r="D368" t="n">
+        <v>147</v>
+      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>7</v>
+      </c>
+      <c r="D369" t="n">
+        <v>147</v>
+      </c>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>7</v>
+      </c>
+      <c r="D370" t="n">
+        <v>147</v>
+      </c>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>7</v>
+      </c>
+      <c r="D371" t="n">
+        <v>147</v>
+      </c>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>7</v>
+      </c>
+      <c r="D372" t="n">
+        <v>147</v>
+      </c>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>7</v>
+      </c>
+      <c r="D373" t="n">
+        <v>147</v>
+      </c>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>7</v>
+      </c>
+      <c r="D374" t="n">
+        <v>147</v>
+      </c>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>7</v>
+      </c>
+      <c r="D375" t="n">
+        <v>147</v>
+      </c>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>7</v>
+      </c>
+      <c r="D376" t="n">
+        <v>147</v>
+      </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>7</v>
+      </c>
+      <c r="D377" t="n">
+        <v>147</v>
+      </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>7</v>
+      </c>
+      <c r="D378" t="n">
+        <v>147</v>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>7</v>
+      </c>
+      <c r="D379" t="n">
+        <v>147</v>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>7</v>
+      </c>
+      <c r="D380" t="n">
+        <v>147</v>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>7</v>
+      </c>
+      <c r="D381" t="n">
+        <v>147</v>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>7</v>
+      </c>
+      <c r="D382" t="n">
+        <v>147</v>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>7</v>
+      </c>
+      <c r="D383" t="n">
+        <v>147</v>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>7</v>
+      </c>
+      <c r="D384" t="n">
+        <v>260</v>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>7</v>
+      </c>
+      <c r="D385" t="n">
+        <v>260</v>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>7</v>
+      </c>
+      <c r="D386" t="n">
+        <v>260</v>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>7</v>
+      </c>
+      <c r="D387" t="n">
+        <v>260</v>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>7</v>
+      </c>
+      <c r="D388" t="n">
+        <v>260</v>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>7</v>
+      </c>
+      <c r="D389" t="n">
+        <v>260</v>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>7</v>
+      </c>
+      <c r="D390" t="n">
+        <v>260</v>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>7</v>
+      </c>
+      <c r="D391" t="n">
+        <v>260</v>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>7</v>
+      </c>
+      <c r="D392" t="n">
+        <v>260</v>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>7</v>
+      </c>
+      <c r="D393" t="n">
+        <v>260</v>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>p199</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>8</v>
+      </c>
+      <c r="D394" t="n">
+        <v>144</v>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>8</v>
+      </c>
+      <c r="D395" t="n">
+        <v>144</v>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>8</v>
+      </c>
+      <c r="D396" t="n">
+        <v>144</v>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>8</v>
+      </c>
+      <c r="D397" t="n">
+        <v>144</v>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>8</v>
+      </c>
+      <c r="D398" t="n">
+        <v>144</v>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>8</v>
+      </c>
+      <c r="D399" t="n">
+        <v>144</v>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>8</v>
+      </c>
+      <c r="D400" t="n">
+        <v>144</v>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>8</v>
+      </c>
+      <c r="D401" t="n">
+        <v>144</v>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>8</v>
+      </c>
+      <c r="D402" t="n">
+        <v>260</v>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>8</v>
+      </c>
+      <c r="D403" t="n">
+        <v>260</v>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>8</v>
+      </c>
+      <c r="D404" t="n">
+        <v>260</v>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>8</v>
+      </c>
+      <c r="D405" t="n">
+        <v>260</v>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>p207</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>7</v>
+      </c>
+      <c r="D406" t="n">
+        <v>139</v>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>7</v>
+      </c>
+      <c r="D407" t="n">
+        <v>139</v>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>7</v>
+      </c>
+      <c r="D408" t="n">
+        <v>139</v>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>7</v>
+      </c>
+      <c r="D409" t="n">
+        <v>139</v>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>7</v>
+      </c>
+      <c r="D410" t="n">
+        <v>139</v>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>7</v>
+      </c>
+      <c r="D411" t="n">
+        <v>139</v>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>7</v>
+      </c>
+      <c r="D412" t="n">
+        <v>139</v>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>7</v>
+      </c>
+      <c r="D413" t="n">
+        <v>139</v>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>p212</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>12</v>
+      </c>
+      <c r="D414" t="n">
+        <v>90</v>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>12</v>
+      </c>
+      <c r="D415" t="n">
+        <v>90</v>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>12</v>
+      </c>
+      <c r="D416" t="n">
+        <v>90</v>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>12</v>
+      </c>
+      <c r="D417" t="n">
+        <v>90</v>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>12</v>
+      </c>
+      <c r="D418" t="n">
+        <v>90</v>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>12</v>
+      </c>
+      <c r="D419" t="n">
+        <v>90</v>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>12</v>
+      </c>
+      <c r="D420" t="n">
+        <v>90</v>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>12</v>
+      </c>
+      <c r="D421" t="n">
+        <v>90</v>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>12</v>
+      </c>
+      <c r="D422" t="n">
+        <v>90</v>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>12</v>
+      </c>
+      <c r="D423" t="n">
+        <v>90</v>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>12</v>
+      </c>
+      <c r="D424" t="n">
+        <v>90</v>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>12</v>
+      </c>
+      <c r="D425" t="n">
+        <v>90</v>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>12</v>
+      </c>
+      <c r="D426" t="n">
+        <v>90</v>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>12</v>
+      </c>
+      <c r="D427" t="n">
+        <v>90</v>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>12</v>
+      </c>
+      <c r="D428" t="n">
+        <v>90</v>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>12</v>
+      </c>
+      <c r="D429" t="n">
+        <v>90</v>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>12</v>
+      </c>
+      <c r="D430" t="n">
+        <v>90</v>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>12</v>
+      </c>
+      <c r="D431" t="n">
+        <v>90</v>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>12</v>
+      </c>
+      <c r="D432" t="n">
+        <v>90</v>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>12</v>
+      </c>
+      <c r="D433" t="n">
+        <v>90</v>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>12</v>
+      </c>
+      <c r="D434" t="n">
+        <v>90</v>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>12</v>
+      </c>
+      <c r="D435" t="n">
+        <v>90</v>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>12</v>
+      </c>
+      <c r="D436" t="n">
+        <v>90</v>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>12</v>
+      </c>
+      <c r="D437" t="n">
+        <v>90</v>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>p183</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>7</v>
+      </c>
+      <c r="D438" t="n">
+        <v>110</v>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>7</v>
+      </c>
+      <c r="D439" t="n">
+        <v>110</v>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>7</v>
+      </c>
+      <c r="D440" t="n">
+        <v>110</v>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>7</v>
+      </c>
+      <c r="D441" t="n">
+        <v>110</v>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>7</v>
+      </c>
+      <c r="D442" t="n">
+        <v>110</v>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>7</v>
+      </c>
+      <c r="D443" t="n">
+        <v>110</v>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>p184</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>7</v>
+      </c>
+      <c r="D444" t="n">
+        <v>110</v>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>7</v>
+      </c>
+      <c r="D445" t="n">
+        <v>110</v>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>7</v>
+      </c>
+      <c r="D446" t="n">
+        <v>110</v>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>7</v>
+      </c>
+      <c r="D447" t="n">
+        <v>110</v>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>7</v>
+      </c>
+      <c r="D448" t="n">
+        <v>110</v>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>7</v>
+      </c>
+      <c r="D449" t="n">
+        <v>110</v>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>p195</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>p202</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>12</v>
+      </c>
+      <c r="D450" t="n">
+        <v>330</v>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>12</v>
+      </c>
+      <c r="D451" t="n">
+        <v>330</v>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>12</v>
+      </c>
+      <c r="D452" t="n">
+        <v>330</v>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>12</v>
+      </c>
+      <c r="D453" t="n">
+        <v>330</v>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>p182</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
         <is>
           <t>CO010</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -17048,7 +17048,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -17201,7 +17201,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>429</v>
+        <v>300</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>p176</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -17263,7 +17263,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -17298,19 +17298,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p176</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -17540,7 +17540,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17570,16 +17570,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PL14mm</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>BE021</t>
@@ -17602,7 +17603,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -17635,13 +17636,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>12</v>
-      </c>
       <c r="D14" t="n">
         <v>250</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PL14mm</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>BE021</t>
@@ -17664,7 +17666,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -17674,14 +17676,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
@@ -17691,7 +17693,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>p123</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -17723,12 +17725,12 @@
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -17743,12 +17745,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17761,13 +17763,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
       <c r="D17" t="n">
-        <v>533.9</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17775,7 +17778,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17790,7 +17793,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -17824,10 +17827,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>533.9</v>
+        <v>200</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
@@ -17837,7 +17840,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17865,22 +17868,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
       <c r="D19" t="n">
         <v>140</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17890,12 +17892,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17908,14 +17910,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
       <c r="D20" t="n">
         <v>140</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17923,7 +17924,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -17938,7 +17939,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17948,14 +17949,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
@@ -17965,7 +17966,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -17994,10 +17995,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -18007,7 +18008,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -18052,7 +18053,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -18094,24 +18095,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>140</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>438.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -18121,12 +18123,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18138,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -18148,12 +18150,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -18163,12 +18165,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18180,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -18195,7 +18197,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>p83</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -18240,7 +18242,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -18331,7 +18333,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
@@ -18393,7 +18395,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -18403,7 +18405,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -18435,7 +18437,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -18445,7 +18447,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -18470,24 +18472,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18497,12 +18499,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18515,14 +18517,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
       <c r="D33" t="n">
-        <v>116</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -18530,7 +18531,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -18545,7 +18546,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18555,16 +18556,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>313</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -18572,7 +18574,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -18587,7 +18589,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18600,13 +18602,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>7</v>
-      </c>
       <c r="D35" t="n">
-        <v>60</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -18614,7 +18617,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -18629,7 +18632,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18646,17 +18649,17 @@
         <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -18666,12 +18669,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18693,12 +18696,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -18708,12 +18711,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18785,7 +18788,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -18827,14 +18830,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -18844,7 +18847,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -18873,10 +18876,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
@@ -18886,7 +18889,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -18911,16 +18914,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>220</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -18928,7 +18932,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -18943,7 +18947,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18956,14 +18960,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
       <c r="D43" t="n">
-        <v>116</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -18971,7 +18974,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -18986,7 +18989,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19000,7 +19003,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
         <v>60</v>
@@ -19013,7 +19016,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -19045,17 +19048,17 @@
         <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -19065,12 +19068,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19087,12 +19090,12 @@
         <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -19107,12 +19110,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19122,14 +19125,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>16</v>
       </c>
       <c r="D47" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
@@ -19139,7 +19142,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -19191,12 +19194,12 @@
         <v>16</v>
       </c>
       <c r="D48" t="n">
-        <v>405</v>
+        <v>158</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -19211,12 +19214,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19226,24 +19229,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>164.5</v>
+        <v>158</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -19253,12 +19256,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19268,24 +19271,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D50" t="n">
-        <v>164.5</v>
+        <v>158</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -19295,12 +19298,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19310,24 +19313,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -19337,12 +19340,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19466,7 @@
         <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
@@ -19473,7 +19476,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -19498,14 +19501,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
@@ -19515,7 +19518,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p169</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -19540,14 +19543,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -19582,16 +19585,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>10</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D57" t="n">
-        <v>350</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PL12mm</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -19599,7 +19603,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>p169</t>
+          <t>p184</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -19614,7 +19618,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -19624,7 +19628,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -19641,7 +19645,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>p184</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -19666,7 +19670,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -19708,11 +19712,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
         <v>139</v>
@@ -19725,7 +19729,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>p196</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19757,7 +19761,7 @@
         <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -19796,7 +19800,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
         <v>139</v>
@@ -19809,7 +19813,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19834,11 +19838,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
         <v>139</v>
@@ -19851,7 +19855,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -20002,14 +20006,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -20048,7 +20052,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D68" t="n">
         <v>139</v>
@@ -20061,7 +20065,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p207</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20086,7 +20090,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -20135,7 +20139,7 @@
         <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -20177,7 +20181,7 @@
         <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -20216,10 +20220,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
@@ -20229,7 +20233,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20392,7 +20396,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -20434,7 +20438,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -20476,7 +20480,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -20518,7 +20522,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -20548,25 +20552,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>12</v>
       </c>
       <c r="D80" t="n">
-        <v>324</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -20581,7 +20584,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -20594,22 +20597,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C81" t="n">
+        <v>12</v>
+      </c>
       <c r="D81" t="n">
-        <v>324</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -20624,7 +20626,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -20637,23 +20639,24 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>9</v>
-      </c>
       <c r="D82" t="n">
-        <v>110</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>p194</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>p195</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>361-RC3210-S-01-CO010</t>
@@ -20666,7 +20669,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -20676,11 +20679,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D83" t="n">
         <v>110</v>
@@ -20693,7 +20696,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>p196</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="焊缝统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常报告" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抽检清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="焊缝统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="异常报告" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="抽检清单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17052,10 +17052,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>461</v>
+        <v>220</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -17110,14 +17110,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
@@ -17164,12 +17164,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BE018</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -17263,7 +17263,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -17340,14 +17340,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>220</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -17402,14 +17402,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -17456,7 +17456,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17486,14 +17486,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
@@ -17528,19 +17528,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17636,14 +17636,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
       <c r="D14" t="n">
-        <v>250</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PL14mm</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>BE021</t>
@@ -17666,7 +17665,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17675,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -17718,7 +17717,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -17763,14 +17762,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
       <c r="D17" t="n">
-        <v>140</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>533.9</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17778,7 +17776,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17793,7 +17791,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -17823,16 +17821,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>6</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>200</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17840,7 +17839,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17855,7 +17854,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -17868,21 +17867,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>7</v>
-      </c>
       <c r="D19" t="n">
         <v>140</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17892,12 +17892,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -17907,7 +17907,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -17919,12 +17919,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -17934,12 +17934,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17949,16 +17949,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17966,7 +17967,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -17981,7 +17982,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -17991,14 +17992,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -18008,7 +18009,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -18099,7 +18100,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>438.9</v>
+        <v>140</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -18150,14 +18151,14 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>p42</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>p43</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>361-RC3210-S-01-BE023</t>
@@ -18165,12 +18166,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18180,14 +18181,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
@@ -18197,7 +18198,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -18242,14 +18243,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
@@ -18259,7 +18260,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -18291,7 +18292,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -18333,7 +18334,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
@@ -18343,7 +18344,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -18395,7 +18396,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -18405,7 +18406,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -18437,7 +18438,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -18447,7 +18448,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -18479,7 +18480,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
@@ -18489,7 +18490,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18514,14 +18515,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
@@ -18531,7 +18532,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -18556,17 +18557,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
       </c>
       <c r="D34" t="n">
         <v>220</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18602,14 +18602,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
       <c r="D35" t="n">
-        <v>116</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -18617,7 +18616,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -18632,7 +18631,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18642,24 +18641,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -18669,12 +18668,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18726,14 +18725,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
@@ -18743,7 +18742,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -18795,17 +18794,17 @@
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>115</v>
+        <v>90.5</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -18815,12 +18814,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18834,10 +18833,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -18872,16 +18871,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D41" t="n">
-        <v>115</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18917,14 +18917,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
       <c r="D42" t="n">
-        <v>116</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -18932,7 +18931,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -18947,7 +18946,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18963,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
@@ -18999,24 +18998,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -19026,12 +19025,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19041,7 +19040,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -19053,7 +19052,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -19068,12 +19067,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19125,7 +19124,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -19187,14 +19186,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>16</v>
       </c>
       <c r="D48" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
@@ -19204,7 +19203,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -19278,12 +19277,12 @@
         <v>16</v>
       </c>
       <c r="D50" t="n">
-        <v>158</v>
+        <v>405</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -19298,12 +19297,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19317,10 +19316,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>38</v>
+        <v>164.5</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -19330,7 +19329,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -19355,24 +19354,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>164.5</v>
+        <v>400</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -19382,12 +19381,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19397,14 +19396,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
@@ -19414,7 +19413,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -19459,14 +19458,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
@@ -19476,7 +19475,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p169</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -19501,14 +19500,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
@@ -19543,14 +19542,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -19560,7 +19559,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>p169</t>
+          <t>p184</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -19588,14 +19587,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
       <c r="D57" t="n">
         <v>139</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -19603,7 +19601,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>p184</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -19618,7 +19616,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19630,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
         <v>139</v>
@@ -19645,7 +19643,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -19670,11 +19668,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
         <v>139</v>
@@ -19687,7 +19685,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p196</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -19712,14 +19710,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
@@ -19729,7 +19727,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19761,7 +19759,7 @@
         <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -19800,7 +19798,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D62" t="n">
         <v>139</v>
@@ -19813,7 +19811,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19841,13 +19839,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>7</v>
-      </c>
       <c r="D63" t="n">
-        <v>139</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>260</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PL12mm</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -19855,7 +19854,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -19870,7 +19869,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -19922,7 +19921,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -19971,7 +19970,7 @@
         <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -20013,7 +20012,7 @@
         <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -20052,7 +20051,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D68" t="n">
         <v>139</v>
@@ -20065,7 +20064,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20178,10 +20177,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
@@ -20191,7 +20190,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20216,24 +20215,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>p212</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20243,12 +20242,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -20258,24 +20257,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>p212</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20285,12 +20284,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -20300,24 +20299,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>p212</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -20327,12 +20326,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -20354,7 +20353,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -20384,7 +20383,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -20396,7 +20395,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -20426,7 +20425,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -20438,7 +20437,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -20480,7 +20479,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -20522,7 +20521,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>p182</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -20552,24 +20551,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p196</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -20601,17 +20600,17 @@
         <v>12</v>
       </c>
       <c r="D81" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -20636,25 +20635,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>12</v>
       </c>
       <c r="D82" t="n">
-        <v>324</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -20669,7 +20667,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -20679,7 +20677,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C83" t="n">

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -17048,14 +17048,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -17114,10 +17114,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
@@ -17127,7 +17127,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -17152,26 +17152,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
+          <t>BE018</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>p52</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>p53</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>361-RC3210-S-01-BE018</t>
@@ -17179,12 +17179,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17194,14 +17194,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -17256,14 +17256,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>220</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -17298,19 +17298,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BE019</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17344,10 +17344,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>220</v>
+        <v>445</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>220</v>
+        <v>445</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -17448,20 +17448,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17498,7 +17498,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -17513,12 +17513,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17528,19 +17528,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17570,17 +17570,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>250</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PL14mm</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>BE021</t>
@@ -17603,7 +17602,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -17633,14 +17632,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
@@ -17650,7 +17649,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -17675,24 +17674,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -17702,12 +17701,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17724,12 +17723,12 @@
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -17744,12 +17743,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17762,13 +17761,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
       <c r="D17" t="n">
-        <v>533.9</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -17824,22 +17824,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
       <c r="D18" t="n">
         <v>140</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17849,12 +17848,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17864,17 +17863,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>140</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17882,7 +17880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17897,7 +17895,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17907,26 +17905,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>p18</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>p19</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>361-RC3210-S-01-BE022</t>
@@ -17934,12 +17932,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17992,16 +17990,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>440</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>438.9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -18009,7 +18008,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -18024,7 +18023,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -18054,7 +18053,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -18100,7 +18099,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>140</v>
+        <v>438.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -18181,7 +18180,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -18243,14 +18242,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
@@ -18260,7 +18259,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>p83</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -18292,7 +18291,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -18396,7 +18395,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -18406,7 +18405,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -18473,14 +18472,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>115</v>
+        <v>90.5</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
@@ -18490,7 +18489,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18519,10 +18518,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
@@ -18532,7 +18531,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -18599,14 +18598,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>313</v>
+        <v>115</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
@@ -18616,7 +18615,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -18641,7 +18640,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -18658,7 +18657,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -18683,7 +18682,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -18695,7 +18694,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -18710,12 +18709,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18731,7 @@
         <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>115</v>
+        <v>250</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
@@ -18742,7 +18741,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -18787,24 +18786,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -18814,12 +18813,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18845,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -18874,22 +18873,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
       <c r="D41" t="n">
-        <v>116</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -18899,12 +18897,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18921,7 +18919,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
@@ -18931,7 +18929,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -18959,13 +18957,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>7</v>
-      </c>
       <c r="D43" t="n">
-        <v>60</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -18973,7 +18972,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -18988,7 +18987,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18998,24 +18997,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D44" t="n">
-        <v>90</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -19025,12 +19025,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -19040,19 +19040,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>90.5</v>
+        <v>60</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -19067,12 +19067,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19190,20 +19190,20 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -19213,12 +19213,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19228,24 +19228,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>158</v>
+        <v>343</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -19255,12 +19255,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19316,10 +19316,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>164.5</v>
+        <v>308</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -19358,20 +19358,20 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>400</v>
+        <v>197</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -19461,13 +19461,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>10</v>
-      </c>
       <c r="D54" t="n">
-        <v>262</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PL12mm</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -19475,7 +19476,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>p169</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -19490,7 +19491,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -19507,7 +19508,7 @@
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
@@ -19549,7 +19550,7 @@
         <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
@@ -19559,7 +19560,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>p184</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -19584,11 +19585,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
         <v>139</v>
@@ -19601,7 +19602,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -19626,14 +19627,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
@@ -19643,7 +19644,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -19668,11 +19669,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
         <v>139</v>
@@ -19685,7 +19686,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>p196</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -19713,13 +19714,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>12</v>
-      </c>
       <c r="D60" t="n">
-        <v>110</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>260</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PL12mm</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -19727,7 +19729,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p198</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19742,7 +19744,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -19752,14 +19754,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -19769,7 +19771,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -19794,11 +19796,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
         <v>139</v>
@@ -19811,7 +19813,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19839,14 +19841,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
       <c r="D63" t="n">
         <v>260</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -19854,7 +19855,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -19869,7 +19870,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19886,7 +19887,7 @@
         <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -19928,7 +19929,7 @@
         <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
@@ -19963,14 +19964,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -19980,7 +19981,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -20005,14 +20006,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -20022,7 +20023,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p207</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -20051,7 +20052,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D68" t="n">
         <v>139</v>
@@ -20064,7 +20065,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p207</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20089,14 +20090,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
@@ -20135,10 +20136,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D70" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
@@ -20148,7 +20149,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>p207</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20222,17 +20223,17 @@
         <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>sp23</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p212</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20242,12 +20243,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -20257,7 +20258,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -20311,7 +20312,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20353,7 +20354,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -20395,7 +20396,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>p182</t>
+          <t>sp23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -20425,7 +20426,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -20509,26 +20510,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D79" t="n">
-        <v>90</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PL20mm</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>sp23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>p182</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>361-RC3210-S-01-CO010</t>
@@ -20541,7 +20543,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -20554,13 +20556,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>9</v>
-      </c>
       <c r="D80" t="n">
-        <v>110</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>p195</t>
@@ -20568,7 +20571,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>p196</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -20583,7 +20586,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -20596,13 +20599,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>12</v>
-      </c>
       <c r="D81" t="n">
         <v>110</v>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>p195</t>
@@ -20610,7 +20614,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>p212</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -20625,7 +20629,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -20635,11 +20639,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
         <v>110</v>
@@ -20652,7 +20656,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>p212</t>
+          <t>p196</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -20681,7 +20685,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
         <v>110</v>
@@ -20694,7 +20698,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>p212</t>
+          <t>p196</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N385"/>
+  <dimension ref="A1:N233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,8 +446,8 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10487,6424 +10487,6 @@
         </is>
       </c>
       <c r="J233" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>233</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
-        <v>12</v>
-      </c>
-      <c r="D234" t="n">
-        <v>110</v>
-      </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>LJ, TJ</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>CJP, FW, PP</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>LJ:42, TJ:110</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>CJP:14, FW:106, PP:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>234</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C235" t="n">
-        <v>12</v>
-      </c>
-      <c r="D235" t="n">
-        <v>110</v>
-      </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>235</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>12</v>
-      </c>
-      <c r="D236" t="n">
-        <v>110</v>
-      </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>236</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>12</v>
-      </c>
-      <c r="D237" t="n">
-        <v>110</v>
-      </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>237</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>12</v>
-      </c>
-      <c r="D238" t="n">
-        <v>110</v>
-      </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>238</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>12</v>
-      </c>
-      <c r="D239" t="n">
-        <v>110</v>
-      </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>239</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>8</v>
-      </c>
-      <c r="D240" t="n">
-        <v>200</v>
-      </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>240</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
-        <v>8</v>
-      </c>
-      <c r="D241" t="n">
-        <v>200</v>
-      </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>241</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C242" t="n">
-        <v>8</v>
-      </c>
-      <c r="D242" t="n">
-        <v>200</v>
-      </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>242</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C243" t="n">
-        <v>12</v>
-      </c>
-      <c r="D243" t="n">
-        <v>200</v>
-      </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>243</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
-        <v>12</v>
-      </c>
-      <c r="D244" t="n">
-        <v>200</v>
-      </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>244</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
-        <v>12</v>
-      </c>
-      <c r="D245" t="n">
-        <v>200</v>
-      </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>245</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>139</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>246</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>139</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>247</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>10</v>
-      </c>
-      <c r="D248" t="n">
-        <v>350</v>
-      </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>248</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>10</v>
-      </c>
-      <c r="D249" t="n">
-        <v>350</v>
-      </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>249</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>10</v>
-      </c>
-      <c r="D250" t="n">
-        <v>350</v>
-      </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>250</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>10</v>
-      </c>
-      <c r="D251" t="n">
-        <v>350</v>
-      </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>251</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
-        <v>10</v>
-      </c>
-      <c r="D252" t="n">
-        <v>262</v>
-      </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>252</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>10</v>
-      </c>
-      <c r="D253" t="n">
-        <v>262</v>
-      </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>253</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>139</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>p184</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>254</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>9</v>
-      </c>
-      <c r="D255" t="n">
-        <v>139</v>
-      </c>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>p184</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>255</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>9</v>
-      </c>
-      <c r="D256" t="n">
-        <v>139</v>
-      </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>p184</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>256</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C257" t="n">
-        <v>9</v>
-      </c>
-      <c r="D257" t="n">
-        <v>139</v>
-      </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>257</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>9</v>
-      </c>
-      <c r="D258" t="n">
-        <v>139</v>
-      </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>9</v>
-      </c>
-      <c r="D259" t="n">
-        <v>139</v>
-      </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
-        <v>259</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C260" t="n">
-        <v>9</v>
-      </c>
-      <c r="D260" t="n">
-        <v>139</v>
-      </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>260</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C261" t="n">
-        <v>9</v>
-      </c>
-      <c r="D261" t="n">
-        <v>260</v>
-      </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>261</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C262" t="n">
-        <v>9</v>
-      </c>
-      <c r="D262" t="n">
-        <v>260</v>
-      </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>262</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
-        <v>12</v>
-      </c>
-      <c r="D263" t="n">
-        <v>139</v>
-      </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
-        <v>263</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>12</v>
-      </c>
-      <c r="D264" t="n">
-        <v>139</v>
-      </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
-        <v>264</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>12</v>
-      </c>
-      <c r="D265" t="n">
-        <v>139</v>
-      </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
-        <v>265</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
-        <v>12</v>
-      </c>
-      <c r="D266" t="n">
-        <v>139</v>
-      </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
-        <v>266</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
-        <v>12</v>
-      </c>
-      <c r="D267" t="n">
-        <v>139</v>
-      </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>267</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>12</v>
-      </c>
-      <c r="D268" t="n">
-        <v>139</v>
-      </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>268</v>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
-        <v>9</v>
-      </c>
-      <c r="D269" t="n">
-        <v>139</v>
-      </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
-        <v>269</v>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C270" t="n">
-        <v>9</v>
-      </c>
-      <c r="D270" t="n">
-        <v>139</v>
-      </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
-        <v>270</v>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
-        <v>9</v>
-      </c>
-      <c r="D271" t="n">
-        <v>139</v>
-      </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>271</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>9</v>
-      </c>
-      <c r="D272" t="n">
-        <v>139</v>
-      </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>272</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>12</v>
-      </c>
-      <c r="D273" t="n">
-        <v>110</v>
-      </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>273</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>12</v>
-      </c>
-      <c r="D274" t="n">
-        <v>110</v>
-      </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>274</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>12</v>
-      </c>
-      <c r="D275" t="n">
-        <v>110</v>
-      </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>275</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>12</v>
-      </c>
-      <c r="D276" t="n">
-        <v>110</v>
-      </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>276</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>12</v>
-      </c>
-      <c r="D277" t="n">
-        <v>110</v>
-      </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>277</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>12</v>
-      </c>
-      <c r="D278" t="n">
-        <v>110</v>
-      </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>278</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>12</v>
-      </c>
-      <c r="D279" t="n">
-        <v>139</v>
-      </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>279</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>12</v>
-      </c>
-      <c r="D280" t="n">
-        <v>139</v>
-      </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>280</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>12</v>
-      </c>
-      <c r="D281" t="n">
-        <v>139</v>
-      </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>281</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>12</v>
-      </c>
-      <c r="D282" t="n">
-        <v>139</v>
-      </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>282</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>12</v>
-      </c>
-      <c r="D283" t="n">
-        <v>139</v>
-      </c>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>283</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>12</v>
-      </c>
-      <c r="D284" t="n">
-        <v>139</v>
-      </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>284</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D285" t="n">
-        <v>260</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>285</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>7</v>
-      </c>
-      <c r="D286" t="n">
-        <v>139</v>
-      </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>286</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>7</v>
-      </c>
-      <c r="D287" t="n">
-        <v>139</v>
-      </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>287</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>7</v>
-      </c>
-      <c r="D288" t="n">
-        <v>139</v>
-      </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>288</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>7</v>
-      </c>
-      <c r="D289" t="n">
-        <v>139</v>
-      </c>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>289</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>7</v>
-      </c>
-      <c r="D290" t="n">
-        <v>139</v>
-      </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>290</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>7</v>
-      </c>
-      <c r="D291" t="n">
-        <v>139</v>
-      </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>291</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>7</v>
-      </c>
-      <c r="D292" t="n">
-        <v>139</v>
-      </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>292</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>7</v>
-      </c>
-      <c r="D293" t="n">
-        <v>139</v>
-      </c>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>293</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>7</v>
-      </c>
-      <c r="D294" t="n">
-        <v>139</v>
-      </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>294</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>7</v>
-      </c>
-      <c r="D295" t="n">
-        <v>139</v>
-      </c>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>295</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>7</v>
-      </c>
-      <c r="D296" t="n">
-        <v>139</v>
-      </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>296</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>7</v>
-      </c>
-      <c r="D297" t="n">
-        <v>139</v>
-      </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>297</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>7</v>
-      </c>
-      <c r="D298" t="n">
-        <v>139</v>
-      </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>298</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>7</v>
-      </c>
-      <c r="D299" t="n">
-        <v>139</v>
-      </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>299</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>7</v>
-      </c>
-      <c r="D300" t="n">
-        <v>139</v>
-      </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>300</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>7</v>
-      </c>
-      <c r="D301" t="n">
-        <v>139</v>
-      </c>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>301</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>7</v>
-      </c>
-      <c r="D302" t="n">
-        <v>139</v>
-      </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>302</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>7</v>
-      </c>
-      <c r="D303" t="n">
-        <v>139</v>
-      </c>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>303</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>7</v>
-      </c>
-      <c r="D304" t="n">
-        <v>139</v>
-      </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>304</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>7</v>
-      </c>
-      <c r="D305" t="n">
-        <v>139</v>
-      </c>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>305</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>7</v>
-      </c>
-      <c r="D306" t="n">
-        <v>260</v>
-      </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>306</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>7</v>
-      </c>
-      <c r="D307" t="n">
-        <v>260</v>
-      </c>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>307</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>7</v>
-      </c>
-      <c r="D308" t="n">
-        <v>260</v>
-      </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>308</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>7</v>
-      </c>
-      <c r="D309" t="n">
-        <v>260</v>
-      </c>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>309</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>7</v>
-      </c>
-      <c r="D310" t="n">
-        <v>260</v>
-      </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>310</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>7</v>
-      </c>
-      <c r="D311" t="n">
-        <v>260</v>
-      </c>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>311</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>7</v>
-      </c>
-      <c r="D312" t="n">
-        <v>260</v>
-      </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>312</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>7</v>
-      </c>
-      <c r="D313" t="n">
-        <v>260</v>
-      </c>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>313</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>7</v>
-      </c>
-      <c r="D314" t="n">
-        <v>260</v>
-      </c>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>314</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>7</v>
-      </c>
-      <c r="D315" t="n">
-        <v>260</v>
-      </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>315</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>12</v>
-      </c>
-      <c r="D316" t="n">
-        <v>139</v>
-      </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>316</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>12</v>
-      </c>
-      <c r="D317" t="n">
-        <v>139</v>
-      </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>317</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>12</v>
-      </c>
-      <c r="D318" t="n">
-        <v>139</v>
-      </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>318</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>12</v>
-      </c>
-      <c r="D319" t="n">
-        <v>139</v>
-      </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>319</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>12</v>
-      </c>
-      <c r="D320" t="n">
-        <v>139</v>
-      </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>320</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>12</v>
-      </c>
-      <c r="D321" t="n">
-        <v>139</v>
-      </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>321</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>12</v>
-      </c>
-      <c r="D322" t="n">
-        <v>139</v>
-      </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>322</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>12</v>
-      </c>
-      <c r="D323" t="n">
-        <v>139</v>
-      </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>323</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>9</v>
-      </c>
-      <c r="D324" t="n">
-        <v>139</v>
-      </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>324</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>9</v>
-      </c>
-      <c r="D325" t="n">
-        <v>139</v>
-      </c>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>325</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C326" t="n">
-        <v>9</v>
-      </c>
-      <c r="D326" t="n">
-        <v>139</v>
-      </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>326</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>9</v>
-      </c>
-      <c r="D327" t="n">
-        <v>139</v>
-      </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>327</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C328" t="n">
-        <v>9</v>
-      </c>
-      <c r="D328" t="n">
-        <v>139</v>
-      </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>328</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C329" t="n">
-        <v>9</v>
-      </c>
-      <c r="D329" t="n">
-        <v>139</v>
-      </c>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>329</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C330" t="n">
-        <v>9</v>
-      </c>
-      <c r="D330" t="n">
-        <v>139</v>
-      </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>330</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>9</v>
-      </c>
-      <c r="D331" t="n">
-        <v>139</v>
-      </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>331</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>9</v>
-      </c>
-      <c r="D332" t="n">
-        <v>260</v>
-      </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>332</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C333" t="n">
-        <v>9</v>
-      </c>
-      <c r="D333" t="n">
-        <v>260</v>
-      </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>333</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C334" t="n">
-        <v>9</v>
-      </c>
-      <c r="D334" t="n">
-        <v>260</v>
-      </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>334</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>9</v>
-      </c>
-      <c r="D335" t="n">
-        <v>260</v>
-      </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>335</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C336" t="n">
-        <v>12</v>
-      </c>
-      <c r="D336" t="n">
-        <v>139</v>
-      </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>336</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C337" t="n">
-        <v>12</v>
-      </c>
-      <c r="D337" t="n">
-        <v>139</v>
-      </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>337</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C338" t="n">
-        <v>12</v>
-      </c>
-      <c r="D338" t="n">
-        <v>139</v>
-      </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>338</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>12</v>
-      </c>
-      <c r="D339" t="n">
-        <v>139</v>
-      </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>339</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>12</v>
-      </c>
-      <c r="D340" t="n">
-        <v>139</v>
-      </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>340</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>12</v>
-      </c>
-      <c r="D341" t="n">
-        <v>139</v>
-      </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>341</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>12</v>
-      </c>
-      <c r="D342" t="n">
-        <v>139</v>
-      </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>342</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>12</v>
-      </c>
-      <c r="D343" t="n">
-        <v>139</v>
-      </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>343</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>12</v>
-      </c>
-      <c r="D344" t="n">
-        <v>90</v>
-      </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>344</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>12</v>
-      </c>
-      <c r="D345" t="n">
-        <v>90</v>
-      </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>345</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C346" t="n">
-        <v>12</v>
-      </c>
-      <c r="D346" t="n">
-        <v>90</v>
-      </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>346</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>12</v>
-      </c>
-      <c r="D347" t="n">
-        <v>90</v>
-      </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>347</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>12</v>
-      </c>
-      <c r="D348" t="n">
-        <v>90</v>
-      </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>348</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>12</v>
-      </c>
-      <c r="D349" t="n">
-        <v>90</v>
-      </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>349</v>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>12</v>
-      </c>
-      <c r="D350" t="n">
-        <v>90</v>
-      </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>350</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>12</v>
-      </c>
-      <c r="D351" t="n">
-        <v>90</v>
-      </c>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>351</v>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>12</v>
-      </c>
-      <c r="D352" t="n">
-        <v>90</v>
-      </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>352</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>12</v>
-      </c>
-      <c r="D353" t="n">
-        <v>90</v>
-      </c>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>353</v>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>12</v>
-      </c>
-      <c r="D354" t="n">
-        <v>90</v>
-      </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>354</v>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>12</v>
-      </c>
-      <c r="D355" t="n">
-        <v>90</v>
-      </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>355</v>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>12</v>
-      </c>
-      <c r="D356" t="n">
-        <v>90</v>
-      </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>356</v>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>12</v>
-      </c>
-      <c r="D357" t="n">
-        <v>90</v>
-      </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>357</v>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>12</v>
-      </c>
-      <c r="D358" t="n">
-        <v>90</v>
-      </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>358</v>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>12</v>
-      </c>
-      <c r="D359" t="n">
-        <v>90</v>
-      </c>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>359</v>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>12</v>
-      </c>
-      <c r="D360" t="n">
-        <v>90</v>
-      </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>360</v>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>12</v>
-      </c>
-      <c r="D361" t="n">
-        <v>90</v>
-      </c>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>361</v>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>12</v>
-      </c>
-      <c r="D362" t="n">
-        <v>90</v>
-      </c>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>362</v>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>12</v>
-      </c>
-      <c r="D363" t="n">
-        <v>90</v>
-      </c>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>363</v>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>12</v>
-      </c>
-      <c r="D364" t="n">
-        <v>90</v>
-      </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>364</v>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>12</v>
-      </c>
-      <c r="D365" t="n">
-        <v>90</v>
-      </c>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>365</v>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>12</v>
-      </c>
-      <c r="D366" t="n">
-        <v>90</v>
-      </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>366</v>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>12</v>
-      </c>
-      <c r="D367" t="n">
-        <v>90</v>
-      </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
-        <v>367</v>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D368" t="n">
-        <v>330</v>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>PL20mm</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
-        <v>368</v>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D369" t="n">
-        <v>330</v>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>PL20mm</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="n">
-        <v>369</v>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D370" t="n">
-        <v>324</v>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>370</v>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D371" t="n">
-        <v>324</v>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>371</v>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D372" t="n">
-        <v>324</v>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
-        <v>372</v>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D373" t="n">
-        <v>324</v>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>373</v>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D374" t="n">
-        <v>324</v>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I374" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="n">
-        <v>374</v>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D375" t="n">
-        <v>324</v>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>375</v>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D376" t="n">
-        <v>110</v>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
-        <v>376</v>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D377" t="n">
-        <v>110</v>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
-        <v>377</v>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C378" t="n">
-        <v>9</v>
-      </c>
-      <c r="D378" t="n">
-        <v>110</v>
-      </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
-        <v>378</v>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>9</v>
-      </c>
-      <c r="D379" t="n">
-        <v>110</v>
-      </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J379" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
-        <v>379</v>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>12</v>
-      </c>
-      <c r="D380" t="n">
-        <v>110</v>
-      </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="n">
-        <v>380</v>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C381" t="n">
-        <v>12</v>
-      </c>
-      <c r="D381" t="n">
-        <v>110</v>
-      </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>381</v>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>12</v>
-      </c>
-      <c r="D382" t="n">
-        <v>110</v>
-      </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>382</v>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>12</v>
-      </c>
-      <c r="D383" t="n">
-        <v>110</v>
-      </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I383" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>383</v>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C384" t="n">
-        <v>9</v>
-      </c>
-      <c r="D384" t="n">
-        <v>110</v>
-      </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>p184</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>384</v>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C385" t="n">
-        <v>9</v>
-      </c>
-      <c r="D385" t="n">
-        <v>110</v>
-      </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>p184</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
         <is>
           <t>PP</t>
         </is>
@@ -16951,7 +10533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16966,8 +10548,8 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17055,7 +10637,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>300</v>
+        <v>461</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -17065,7 +10647,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -17114,10 +10696,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>140</v>
+        <v>461</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
@@ -17127,7 +10709,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -17152,7 +10734,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -17194,14 +10776,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>429</v>
+        <v>300</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
@@ -17211,7 +10793,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>p176</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -17256,7 +10838,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -17298,24 +10880,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p176</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -17325,12 +10907,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17340,14 +10922,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>300</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -17357,7 +10939,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -17402,14 +10984,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -17419,7 +11001,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -17444,14 +11026,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>300</v>
+        <v>39</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
@@ -17461,7 +11043,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -17486,7 +11068,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -17498,7 +11080,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -17513,12 +11095,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17535,12 +11117,12 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p175</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -17555,12 +11137,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -17570,14 +11152,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
@@ -17632,7 +11214,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -17758,17 +11340,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>140</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>533.9</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -17776,7 +11357,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17791,7 +11372,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -17824,21 +11405,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
       <c r="D18" t="n">
         <v>140</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>BE022</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17848,12 +11430,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -17870,17 +11452,17 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17890,12 +11472,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -17912,7 +11494,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
@@ -17951,7 +11533,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>140</v>
+        <v>438.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -17993,14 +11575,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
       <c r="D22" t="n">
-        <v>438.9</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -18008,7 +11589,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -18023,7 +11604,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -18053,14 +11634,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
@@ -18070,7 +11651,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -18099,7 +11680,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>438.9</v>
+        <v>140</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -18138,11 +11719,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>140</v>
@@ -18155,7 +11736,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -18187,7 +11768,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
@@ -18242,14 +11823,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
@@ -18259,7 +11840,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -18284,7 +11865,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -18333,7 +11914,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
@@ -18388,14 +11969,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>250</v>
+        <v>90.5</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -18405,7 +11986,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -18437,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -18447,7 +12028,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -18472,7 +12053,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -18484,7 +12065,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -18499,12 +12080,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18514,7 +12095,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -18560,10 +12141,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
@@ -18598,16 +12179,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>115</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -18615,7 +12197,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -18630,7 +12212,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -18682,7 +12264,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -18699,7 +12281,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -18731,7 +12313,7 @@
         <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>250</v>
+        <v>308</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
@@ -18741,7 +12323,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -18793,7 +12375,7 @@
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
@@ -18835,7 +12417,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -18870,24 +12452,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -18897,12 +12479,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18912,24 +12494,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -18939,12 +12521,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -18957,14 +12539,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
       <c r="D43" t="n">
         <v>220</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -18972,7 +12553,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -18987,7 +12568,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -18997,17 +12578,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>116</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>PL9mm</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -19015,7 +12595,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -19030,7 +12610,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19040,16 +12620,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -19057,7 +12638,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -19072,7 +12653,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -19094,7 +12675,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -19109,12 +12690,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -19131,7 +12712,7 @@
         <v>16</v>
       </c>
       <c r="D47" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
@@ -19141,7 +12722,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -19186,24 +12767,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -19213,12 +12794,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -19270,14 +12851,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D50" t="n">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
@@ -19287,7 +12868,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -19361,12 +12942,12 @@
         <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>197</v>
+        <v>164.5</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -19381,1339 +12962,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>12</v>
-      </c>
-      <c r="D53" t="n">
-        <v>200</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>LJ, TJ</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>CJP, FW, PP</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>LJ:42, TJ:110</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>CJP:14, FW:106, PP:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>139</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>10</v>
-      </c>
-      <c r="D55" t="n">
-        <v>350</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>p169</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>9</v>
-      </c>
-      <c r="D56" t="n">
-        <v>260</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>p185</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>12</v>
-      </c>
-      <c r="D57" t="n">
-        <v>139</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>p194</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>12</v>
-      </c>
-      <c r="D58" t="n">
-        <v>110</v>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>12</v>
-      </c>
-      <c r="D59" t="n">
-        <v>139</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>260</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>PL12mm</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>p198</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>7</v>
-      </c>
-      <c r="D61" t="n">
-        <v>139</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>7</v>
-      </c>
-      <c r="D62" t="n">
-        <v>139</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>7</v>
-      </c>
-      <c r="D63" t="n">
-        <v>260</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>7</v>
-      </c>
-      <c r="D64" t="n">
-        <v>260</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>7</v>
-      </c>
-      <c r="D65" t="n">
-        <v>260</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>p199</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>12</v>
-      </c>
-      <c r="D66" t="n">
-        <v>139</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>9</v>
-      </c>
-      <c r="D67" t="n">
-        <v>139</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>9</v>
-      </c>
-      <c r="D68" t="n">
-        <v>139</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>9</v>
-      </c>
-      <c r="D69" t="n">
-        <v>260</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>p207</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>12</v>
-      </c>
-      <c r="D70" t="n">
-        <v>139</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>12</v>
-      </c>
-      <c r="D71" t="n">
-        <v>139</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>12</v>
-      </c>
-      <c r="D72" t="n">
-        <v>139</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>CO010</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>p212</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>TJ</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>12</v>
-      </c>
-      <c r="D73" t="n">
-        <v>90</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>12</v>
-      </c>
-      <c r="D74" t="n">
-        <v>90</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>12</v>
-      </c>
-      <c r="D75" t="n">
-        <v>90</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>12</v>
-      </c>
-      <c r="D76" t="n">
-        <v>90</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>12</v>
-      </c>
-      <c r="D77" t="n">
-        <v>90</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>12</v>
-      </c>
-      <c r="D78" t="n">
-        <v>90</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>p183</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>330</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>PL20mm</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>sp23</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>p182</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>324</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>p197</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>110</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>p202</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>9</v>
-      </c>
-      <c r="D82" t="n">
-        <v>110</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>9</v>
-      </c>
-      <c r="D83" t="n">
-        <v>110</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>p195</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>p196</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>361-RC3210-S-01-CO010</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>LJ</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -10630,19 +10630,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BE018</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -10838,24 +10838,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BE019</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10922,14 +10922,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>445</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p118</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -10996,7 +10996,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -11026,14 +11026,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -11080,7 +11080,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BE020</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -11218,10 +11218,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>p123</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11263,12 +11263,12 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>BE021</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -11340,16 +11340,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>12</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>533.9</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -11357,7 +11358,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11372,7 +11373,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -11405,14 +11406,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
       <c r="D18" t="n">
-        <v>140</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -11532,14 +11532,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
       <c r="D21" t="n">
-        <v>438.9</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PL10mm</t>
-        </is>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -11547,7 +11546,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -11562,7 +11561,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CJP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11571,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -11634,14 +11633,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
@@ -11651,7 +11650,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11722,13 +11721,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>6</v>
-      </c>
       <c r="D25" t="n">
-        <v>140</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>438.9</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>p83</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -11865,14 +11865,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -11907,14 +11907,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>115</v>
+        <v>250</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -11969,14 +11969,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -12018,7 +12018,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -12060,17 +12060,17 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -12099,10 +12099,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
@@ -12137,16 +12137,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>115</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -12154,7 +12155,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -12169,7 +12170,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -12225,21 +12226,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>7</v>
-      </c>
       <c r="D36" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -12249,12 +12251,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12266,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -12276,12 +12278,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12291,12 +12293,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12315,7 @@
         <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>308</v>
+        <v>220</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
@@ -12323,7 +12325,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12368,14 +12370,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
@@ -12385,7 +12387,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -12417,7 +12419,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>115</v>
+        <v>90.5</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
@@ -12427,7 +12429,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12459,7 +12461,7 @@
         <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
@@ -12469,7 +12471,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12498,20 +12500,20 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>90.5</v>
+        <v>115</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12521,12 +12523,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -12539,13 +12541,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>7</v>
-      </c>
       <c r="D43" t="n">
-        <v>220</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -12553,7 +12556,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12568,7 +12571,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -12578,16 +12581,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D44" t="n">
-        <v>220</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PL9mm</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -12595,7 +12599,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12610,7 +12614,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>CJP</t>
         </is>
       </c>
     </row>
@@ -12663,24 +12667,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>90.5</v>
+        <v>90</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -12690,12 +12694,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12716,7 @@
         <v>16</v>
       </c>
       <c r="D47" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
@@ -12722,7 +12726,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -12767,24 +12771,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -12794,12 +12798,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LJ</t>
+          <t>TJ</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>FW</t>
         </is>
       </c>
     </row>
@@ -12851,14 +12855,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D50" t="n">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
@@ -12868,7 +12872,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -12900,7 +12904,7 @@
         <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
@@ -12942,12 +12946,12 @@
         <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>164.5</v>
+        <v>197</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -12962,12 +12966,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TJ</t>
+          <t>LJ</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>PP</t>
         </is>
       </c>
     </row>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="欧标焊缝统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="欧标异常报告" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="欧标抽检清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="国标焊缝统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="国标异常报告" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="国标抽检清单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,13 +441,13 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,25 +532,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>838</v>
+        <v>461</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
+          <t>361-RC3210-S-01-BE018</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,22 +565,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>, TJ</t>
+          <t>LJ, TJ</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>, FW</t>
+          <t>FW, PP</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>:34, TJ:4</t>
+          <t>LJ:2, TJ:12</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>:34, FW:4</t>
+          <t>FW:12, PP:2</t>
         </is>
       </c>
     </row>
@@ -594,25 +594,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>838</v>
+        <v>461</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
+          <t>361-RC3210-S-01-BE018</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>838</v>
+        <v>300</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
+          <t>361-RC3210-S-01-BE018</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -678,25 +678,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>838</v>
+        <v>300</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
+          <t>361-RC3210-S-01-BE018</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -720,29 +720,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>48.2</v>
+        <v>220</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -754,29 +762,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>48.2</v>
+        <v>220</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -788,29 +804,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>44.1</v>
+        <v>300</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -822,29 +846,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>44.1</v>
+        <v>300</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -856,29 +888,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -890,29 +930,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -924,29 +972,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -958,29 +1014,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -992,29 +1056,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1026,29 +1098,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1060,29 +1140,57 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>429</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>FW, PP</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>LJ:2, TJ:12</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>FW:12, PP:2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1094,29 +1202,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>429</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1128,29 +1244,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1162,29 +1286,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1196,29 +1328,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1230,29 +1370,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1264,29 +1412,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>44.1</v>
+        <v>220</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1298,29 +1454,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>44.1</v>
+        <v>220</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1332,29 +1496,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1366,29 +1538,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1400,29 +1580,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1434,29 +1622,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1468,29 +1664,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1502,29 +1706,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1536,29 +1748,57 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>FW, PP</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>LJ:4, TJ:18</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>FW:18, PP:4</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1566,33 +1806,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1600,33 +1848,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>445</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1638,29 +1894,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>445</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1672,29 +1936,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1706,29 +1978,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1740,29 +2020,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1774,29 +2062,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1808,29 +2104,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>838</v>
+        <v>300</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1842,29 +2146,4771 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>838</v>
+        <v>300</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="n">
+        <v>140</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>p175</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>140</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>p175</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>140</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>140</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+      <c r="D44" t="n">
+        <v>39</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>39</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" t="n">
+        <v>140</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>p175</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>140</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>p175</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>140</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>140</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" t="n">
+        <v>39</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>39</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>250</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PL14mm</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CJP, FW, PP</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LJ:4, TJ:14</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>CJP:2, FW:12, PP:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>250</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PL14mm</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>172</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>172</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>172</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>172</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>12</v>
+      </c>
+      <c r="D58" t="n">
+        <v>250</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" t="n">
+        <v>250</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" t="n">
+        <v>250</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" t="n">
+        <v>250</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>155</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>155</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>155</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>155</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="n">
+        <v>60</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>60</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>60</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" t="n">
+        <v>60</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>CJP, FW, PP</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>LJ:4, TJ:20</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>CJP:6, FW:14, PP:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>140</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>140</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>200</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>p26</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" t="n">
+        <v>200</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>p26</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+      <c r="D79" t="n">
+        <v>140</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>140</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" t="n">
+        <v>140</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" t="n">
+        <v>140</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" t="n">
+        <v>29</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" t="n">
+        <v>29</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>7</v>
+      </c>
+      <c r="D85" t="n">
+        <v>140</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" t="n">
+        <v>140</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" t="n">
+        <v>140</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
+      <c r="D88" t="n">
+        <v>140</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>29</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>7</v>
+      </c>
+      <c r="D90" t="n">
+        <v>29</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>140</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>140</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>9</v>
+      </c>
+      <c r="D94" t="n">
+        <v>440</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>p43</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>CJP, FW, PP</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>LJ:2, TJ:14</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>CJP:6, FW:8, PP:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>9</v>
+      </c>
+      <c r="D95" t="n">
+        <v>440</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>p43</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>140</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>140</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D99" t="n">
+        <v>140</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>p48</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>6</v>
+      </c>
+      <c r="D100" t="n">
+        <v>140</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>p48</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>140</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>140</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>7</v>
+      </c>
+      <c r="D104" t="n">
+        <v>140</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>p43</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>7</v>
+      </c>
+      <c r="D105" t="n">
+        <v>140</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>p43</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>7</v>
+      </c>
+      <c r="D106" t="n">
+        <v>140</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>7</v>
+      </c>
+      <c r="D107" t="n">
+        <v>140</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>33</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>33</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>6</v>
+      </c>
+      <c r="D110" t="n">
+        <v>150</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>TJ:12</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>FW:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>6</v>
+      </c>
+      <c r="D111" t="n">
+        <v>150</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>6</v>
+      </c>
+      <c r="D112" t="n">
+        <v>232</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>232</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>6</v>
+      </c>
+      <c r="D114" t="n">
+        <v>150</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>6</v>
+      </c>
+      <c r="D115" t="n">
+        <v>150</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D116" t="n">
+        <v>150</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D117" t="n">
+        <v>150</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>6</v>
+      </c>
+      <c r="D118" t="n">
+        <v>232</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>6</v>
+      </c>
+      <c r="D119" t="n">
+        <v>232</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>6</v>
+      </c>
+      <c r="D120" t="n">
+        <v>150</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>6</v>
+      </c>
+      <c r="D121" t="n">
+        <v>150</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" t="n">
+        <v>120</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>p16</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>FW, PP</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>LJ:14, TJ:14</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>FW:14, PP:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>16</v>
+      </c>
+      <c r="D123" t="n">
+        <v>120</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>p16</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" t="n">
+        <v>158</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>16</v>
+      </c>
+      <c r="D125" t="n">
+        <v>158</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>16</v>
+      </c>
+      <c r="D126" t="n">
+        <v>120</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>p16</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>16</v>
+      </c>
+      <c r="D127" t="n">
+        <v>120</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>p16</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>16</v>
+      </c>
+      <c r="D128" t="n">
+        <v>158</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>16</v>
+      </c>
+      <c r="D129" t="n">
+        <v>158</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>6</v>
+      </c>
+      <c r="D130" t="n">
+        <v>38</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>p17</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>6</v>
+      </c>
+      <c r="D131" t="n">
+        <v>38</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>p17</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>10</v>
+      </c>
+      <c r="D132" t="n">
+        <v>343</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>10</v>
+      </c>
+      <c r="D133" t="n">
+        <v>343</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>16</v>
+      </c>
+      <c r="D134" t="n">
+        <v>405</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>16</v>
+      </c>
+      <c r="D135" t="n">
+        <v>405</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>16</v>
+      </c>
+      <c r="D136" t="n">
+        <v>308</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>16</v>
+      </c>
+      <c r="D137" t="n">
+        <v>308</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>16</v>
+      </c>
+      <c r="D138" t="n">
+        <v>405</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>16</v>
+      </c>
+      <c r="D139" t="n">
+        <v>405</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>7</v>
+      </c>
+      <c r="D140" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>7</v>
+      </c>
+      <c r="D141" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>7</v>
+      </c>
+      <c r="D142" t="n">
+        <v>197</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>7</v>
+      </c>
+      <c r="D143" t="n">
+        <v>197</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>7</v>
+      </c>
+      <c r="D144" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>7</v>
+      </c>
+      <c r="D145" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>7</v>
+      </c>
+      <c r="D146" t="n">
+        <v>197</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>7</v>
+      </c>
+      <c r="D147" t="n">
+        <v>197</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>16</v>
+      </c>
+      <c r="D148" t="n">
+        <v>400</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>p16</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>16</v>
+      </c>
+      <c r="D149" t="n">
+        <v>400</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>p16</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1907,7 +6953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1917,13 +6963,13 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2004,51 +7050,59 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>48.2</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>, TJ</t>
+          <t>LJ, TJ</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>, FW</t>
+          <t>FW, PP</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>:34, TJ:4</t>
+          <t>LJ:2, TJ:12</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>:34, FW:4</t>
+          <t>FW:12, PP:2</t>
         </is>
       </c>
     </row>
@@ -2062,29 +7116,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2092,33 +7154,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>44.1</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE018</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE018</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2126,33 +7196,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>429</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p176</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FW, PP</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>LJ:2, TJ:12</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FW:12, PP:2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2164,29 +7262,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2194,33 +7300,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A0101</t>
+          <t>BE019</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE019</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2232,29 +7346,57 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A0008</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p175</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>FW, PP</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>LJ:4, TJ:18</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>FW:18, PP:4</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2266,29 +7408,1190 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>838</v>
+        <v>300</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A0200</t>
+          <t>BE020</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AC0003</t>
+          <t>p118</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8901IR004I01AC0003</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>p118</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BE020</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>p52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE020</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>250</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PL14mm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CJP, FW, PP</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>LJ:4, TJ:14</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CJP:2, FW:12, PP:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>p122</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>155</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BE021</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>p123</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE021</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>140</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CJP, FW, PP</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>LJ:4, TJ:20</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CJP:6, FW:14, PP:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>140</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>p19</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>140</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>p18</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE022</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>440</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>p43</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CJP, FW, PP</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>LJ:2, TJ:14</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>CJP:6, FW:8, PP:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>140</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>p48</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>140</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PL10mm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>p200</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>33</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>p42</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-BE023</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>150</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>TJ:12</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>FW:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>150</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>232</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CO006</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO006</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16</v>
+      </c>
+      <c r="D29" t="n">
+        <v>158</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>p15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>LJ, TJ</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>FW, PP</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>LJ:14, TJ:14</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>FW:14, PP:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>343</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16</v>
+      </c>
+      <c r="D31" t="n">
+        <v>405</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" t="n">
+        <v>308</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" t="n">
+        <v>308</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CO009</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TJ</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>197</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>p143</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>p144</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>361-RC3210-S-01-CO009</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LJ</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
